--- a/results/Int Task Remove ACC -0.5/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0035482875655662325 +/- 0.00070696940681206</t>
+          <t>0.003178031471768028 +/- 0.0008051828664424534</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.007034865782166044 +/- 0.0007532586001686999</t>
+          <t>0.008022215365627916 +/- 0.0010688372771174768</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0024683739586547904 +/- 0.0007169978425561504</t>
+          <t>0.001697007096575176 +/- 0.0008307875358121577</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.004011107682813986 +/- 0.0008506046746121679</t>
+          <t>0.0025609379821043055 +/- 0.0010956668253356912</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0035791422400494265 +/- 0.0008639308855291579</t>
+          <t>0.0033014501697007257 +/- 0.0012268371090447911</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0019746991669238323 +/- 0.0019327935530226144</t>
+          <t>0.0011107682813946585 +/- 0.0018054598998244703</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.0854674483227204e-05 +/- 0.00025629817534462377</t>
+          <t>-3.08546744831828e-05 +/- 0.00029108241691009484</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0015427337241592399 +/- 0.0013378268058425779</t>
+          <t>0.001511879049676057 +/- 0.0011985760320614022</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.013051527306386956 +/- 0.002164450466806002</t>
+          <t>0.009595803764270328 +/- 0.0024273433403538174</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.019654427645788362 +/- 0.002097437136606892</t>
+          <t>0.02295587781548909 +/- 0.002763862471651798</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0011107682813945806 +/- 0.0009678733194296846</t>
+          <t>-0.0012958963282936886 +/- 0.0012170986068075274</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0038876889848812545 +/- 0.0008856957787354125</t>
+          <t>0.0006170934896637115 +/- 0.0007430789619742314</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.008299907435976594 +/- 0.0011985760320613848</t>
+          <t>0.004936747917309503 +/- 0.0013163054000432785</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.0074668312249306255 +/- 0.0022155289195947194</t>
+          <t>0.007096575131132399 +/- 0.0023659721706486506</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.011447084233261384 +/- 0.0024623886087909727</t>
+          <t>0.007867941993212012 +/- 0.0018831465004217356</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0013267510027769713 +/- 0.0008840819982656204</t>
+          <t>0.0026535020055538537 +/- 0.0012123963409063987</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0028077753779698123 +/- 0.001116325363475809</t>
+          <t>0.0006788028386300882 +/- 0.0007405121875964324</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0002468373958655401 +/- 0.0015660077186608608</t>
+          <t>-0.001419315026226431 +/- 0.0006353366331988244</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.0001851280468991634 +/- 0.0009579867137463732</t>
+          <t>0.0059858068497377626 +/- 0.0015744956275437199</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>9.25640234496039e-05 +/- 0.00033940141931505617</t>
+          <t>6.17093489663656e-05 +/- 0.0002308952413930127</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.017432891082999048 +/- 0.002061729573870788</t>
+          <t>-0.007435976550447354 +/- 0.0019536150716787</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.0025917926565874215 +/- 0.000604625669307804</t>
+          <t>0.0015735883986424336 +/- 0.001237653262581382</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.0016352977476087327 +/- 0.0014606356530138395</t>
+          <t>-0.003054612773835208 +/- 0.0010367354283499998</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.0014501697007096137 +/- 0.001023798828943987</t>
+          <t>0.0006788028386300882 +/- 0.0008483632881744894</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.00046282011724769757 +/- 0.0015747979210336104</t>
+          <t>-0.004319654427645747 +/- 0.001226449053647147</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0009256402344954839 +/- 0.0003650774318481547</t>
+          <t>0.0001234186979327312 +/- 0.00015115641732694023</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0029003394014193717 +/- 0.0015377890520675212</t>
+          <t>-0.0003085467448317947 +/- 0.0011210059934949191</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.0040728170317802515 +/- 0.0014458962682949755</t>
+          <t>-0.0029620487503856487 +/- 0.0012661699801717417</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.00030854674483180575 +/- 0.0011544762069651022</t>
+          <t>0.0037025609379821465 +/- 0.0006899314956802643</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0023449552607219372 +/- 0.000678802838630065</t>
+          <t>0.0030854674483184576 +/- 0.0010045554209256139</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00027769207034870067 +/- 0.0005596531054371464</t>
+          <t>0.00030854674483186126 +/- 0.0003902841913197803</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.000431965442764648 +/- 0.0002827877627248492</t>
+          <t>-0.000308546744831828 +/- 0.00039028419131974517</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,272 +1046,272 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.0028694847269361556 +/- 0.0007811779636638337</t>
+          <t>0.00280777537796979 +/- 0.001107764459797356</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.0042579450786793815 +/- 0.0011361896105844989</t>
+          <t>-0.0009873495834618496 +/- 0.0010214714814715908</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0007713668620796699 +/- 0.00037153948098711797</t>
+          <t>-0.0005245294662141076 +/- 0.0004789933568731662</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0001542733724159584 +/- 0.0005894777283105041</t>
+          <t>0.00043196544276461466 +/- 0.0008302143811832047</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.0016352977476087106 +/- 0.0014541032604687624</t>
+          <t>-0.004381363776612112 +/- 0.0015290974012173815</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0001542733724159695 +/- 0.0007203096285053302</t>
+          <t>-0.0005553841406972793 +/- 0.0011021642147171667</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.170934896641001e-05 +/- 0.0005308438918261575</t>
+          <t>0.0007713668620796365 +/- 0.0009781467129989123</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.085467448311618e-05 +/- 0.0010088110289584618</t>
+          <t>-0.004905893242826254 +/- 0.0017148649468176815</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0017587164455415416 +/- 0.0009261543363038413</t>
+          <t>-0.001758716445541464 +/- 0.0009859022097297389</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.001882135143474295 +/- 0.0010639271613431993</t>
+          <t>0.002560937982104339 +/- 0.0008284925382349672</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.005152730638691793 +/- 0.0010781490410154972</t>
+          <t>0.0024066646096883916 +/- 0.0013505750464818966</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.006818883060783654 +/- 0.0015331389384517031</t>
+          <t>-0.003208886146251111 +/- 0.0013392492696211369</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0008330762110460354 +/- 0.0005862388151804889</t>
+          <t>-0.0011724776303609686 +/- 0.0014784509164715855</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0009256402344955617 +/- 0.0010777074481069335</t>
+          <t>-0.0018204257945078183 +/- 0.0005245294662141487</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.0008022215365627416 +/- 0.0006646300286497266</t>
+          <t>3.08546744831939e-05 +/- 0.00029108241691011723</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.0003085467448317836 +/- 0.0010417737128129657</t>
+          <t>0.0004011107682814319 +/- 0.0010781490410154953</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0003394014193150663 +/- 0.0009095589616157795</t>
+          <t>0.007682813946312883 +/- 0.0015143957040182822</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0014193150262265196 +/- 0.0009479970068335218</t>
+          <t>0.006325208269052795 +/- 0.001634133005475515</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.002406664609688425 +/- 0.0010121085755542543</t>
+          <t>0.004535637149028137 +/- 0.0012033323048441782</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.0019438444924406272 +/- 0.00033940141931501074</t>
+          <t>0.001357605677260143 +/- 0.0006046256693077802</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0026535020055538983 +/- 0.0007707495215548891</t>
+          <t>0.0009256402344955617 +/- 0.000632332660657806</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>6.17093489663656e-05 +/- 0.00018512804689909678</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.006109225547670493 +/- 0.0012631588701301365</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.0029620487503857263 +/- 0.0013463390453114152</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.0028694847269362 +/- 0.0010603418869139015</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.0001234186979327756 +/- 0.0008416033136060509</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>-0.0002468373958654624 +/- 0.00043196544276455915</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-0.0006479481641468388 +/- 0.0009404350912760336</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.00037025609379823796 +/- 0.0015961144284328932</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.0005245294662141742 +/- 0.0007308064969038701</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.0040111076828139745 +/- 0.0008835434164317196</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.0014810243751928742 +/- 0.0009235809655721021</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-0.010212897253933938 +/- 0.0018015008425788393</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0.0036717062634989417 +/- 0.0008330762110459836</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.0005245294662141852 +/- 0.00024098271138252783</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.003980253008330814 +/- 0.0015017702590111668</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0.0014193150262264975 +/- 0.0010882562226811833</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.0008022215365628416 +/- 0.0003146571745506397</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.009132983647022553 +/- 0.0013743324561135677</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.008269052761493412 +/- 0.0013075976612414123</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.0050293119407590625 +/- 0.0016094787233255233</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>-0.00027769207034864516 +/- 0.000166157507162427</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>6.17093489663878e-05 +/- 0.0007275424944493452</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.0005862388151805287 +/- 0.0005764128877590249</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.0017587164455415305 +/- 0.00033940141931501074</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.0006788028386301104 +/- 0.0007781252831174604</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.004381363776612213 +/- 0.0013784824377469278</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>-0.0005553841406972682 +/- 0.0005655755254496645</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-0.0011724776303609573 +/- 0.0010759392640643467</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.0008639308855292183 +/- 0.0007902652560854953</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-0.013236655353285987 +/- 0.0014435899494340632</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.0004011107682814319 +/- 0.000915817468661272</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.0003702560937982713 +/- 0.0003598242452851431</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>-0.00351743289108295 +/- 0.0016280044379232146</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.0009873495834619383 +/- 0.0008483632881744756</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-0.00021598272138225738 +/- 0.0005172185934662328</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.00635606294353599 +/- 0.0010526826355589142</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.002221536562789295 +/- 0.0006871662280567769</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.0016044430731256276 +/- 0.0014058359456827411</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>6.170934896642111e-05 +/- 0.0003598242452851469</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>-0.0008947855600123011 +/- 0.0004011107682813764</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.0007713668620796477 +/- 0.0009878315701068864</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>6.17093489663989e-05 +/- 0.000431965442764602</t>
+          <t>0.0007096575131132932 +/- 0.00033940141931503704</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.003332304844183931 +/- 0.0016373340526284045</t>
+          <t>-6.170934896633229e-05 +/- 0.0007008834737180322</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>3.0854674483205005e-05 +/- 0.0001661575071624641</t>
+          <t>-3.08546744831828e-05 +/- 9.256402344954838e-05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.0006170934896636449 +/- 0.00047799856170409316</t>
+          <t>3.0854674483216105e-05 +/- 0.0005060542877771437</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.002838630052452973 +/- 0.0007532586001687071</t>
+          <t>0.0018204257945078962 +/- 0.00094043509127603</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0004936747917309914 +/- 0.0012202233837263238</t>
+          <t>0.0042270904041962765 +/- 0.0011548884462951456</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.0002159827213823573 +/- 0.00041510719059162176</t>
+          <t>-0.0008947855600122901 +/- 0.000639071742585865</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.0008330762110460354 +/- 0.000793271220745575</t>
+          <t>0.0018821351434742506 +/- 0.0006823000428107314</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-9.256402344950398e-05 +/- 0.001265041653810541</t>
+          <t>0.012773835236038289 +/- 0.0012123963409064107</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0009873495834619383 +/- 0.0008921217090281364</t>
+          <t>0.0005553841406973681 +/- 0.0008022215365627929</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0019625881631401996 +/- 0.002291510787153576</t>
+          <t>-0.0009812940815701165 +/- 0.0020099318746610085</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.016436675866298645 +/- 0.0013796040330207914</t>
+          <t>-0.00515179392824292 +/- 0.002092452880617219</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0005519779208831954 +/- 0.0017444296416225585</t>
+          <t>0.006531738730450765 +/- 0.001234641038895889</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.0002759889604415422 +/- 0.0010394634318723298</t>
+          <t>0.0022079116835326262 +/- 0.0007359705611775559</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0035571910456915325 +/- 0.0016863204029276403</t>
+          <t>0.002606562404170454 +/- 0.001836089221701676</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.0015026065624041407 +/- 0.0016765332024331909</t>
+          <t>-0.0057651027292242255 +/- 0.002141317417981726</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.199632014722514e-05 +/- 0.0003891008138745753</t>
+          <t>-3.3306690738754695e-17 +/- 0.00027428003403861</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.002422569763876159 +/- 0.0010837532687563486</t>
+          <t>-0.0014719411223551692 +/- 0.0011860827725123405</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.00036798528058881177 +/- 0.0021761662065881795</t>
+          <t>0.0030972094449555065 +/- 0.002329160791384022</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.0059490953695185865 +/- 0.0026670119478882427</t>
+          <t>0.0024532352039251413 +/- 0.0021333979921405693</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.0006133088009812715 +/- 0.0014960209650598695</t>
+          <t>0.008279668813247432 +/- 0.0018703404700370278</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.0008892977614228359 +/- 0.0015237360624109015</t>
+          <t>0.0045998160073596915 +/- 0.0015393928731077854</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.009782275375651683 +/- 0.00128977251424798</t>
+          <t>-0.0032198712051518252 +/- 0.0018103001708856617</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-0.02201778595522842 +/- 0.003897769235310808</t>
+          <t>-0.003986507206378465 +/- 0.0034120039363879032</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.011131554737810467 +/- 0.0026875594743459904</t>
+          <t>0.0002146580803433995 +/- 0.0029190213158938496</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.003649187365838691 +/- 0.002017636816877765</t>
+          <t>0.005581110088929753 +/- 0.0009580189728189972</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.0019932536031891713 +/- 0.0012955921603359406</t>
+          <t>0.0051211284881937606 +/- 0.001599607648665447</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.0032812020852499013 +/- 0.0013510205931868031</t>
+          <t>-0.005489113768782627 +/- 0.0017799168182681734</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.0005826433609321668 +/- 0.0009039805564540788</t>
+          <t>0.002698558724317657 +/- 0.001005901224584893</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-3.066544004904914e-05 +/- 0.0001651384485475149</t>
+          <t>-6.133088009815379e-05 +/- 0.00018399264029440586</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.004569150567310676 +/- 0.0019512957092834276</t>
+          <t>0.0004906470407849972 +/- 0.0021649018822107197</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.005857099049371328 +/- 0.0012970429918771449</t>
+          <t>0.0003373198405396627 +/- 0.0017317151675554122</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.002514566084023351 +/- 0.0013836877243395933</t>
+          <t>0.002637227844219503 +/- 0.0010096337094850727</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.000490647040785075 +/- 0.0011158175650818917</t>
+          <t>0.0021465808034344946 +/- 0.001187667386141486</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00024532352039257076 +/- 0.001270304518688013</t>
+          <t>0.0013492793621588174 +/- 0.0006746396810794112</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0008892977614229136 +/- 0.00053904924352182</t>
+          <t>-3.066544004909355e-05 +/- 0.0006497890248517845</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.002974547684759321 +/- 0.0019202051155416324</t>
+          <t>0.00015332720024527902 +/- 0.0022628102808185564</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.011192885617908654 +/- 0.002613767842669114</t>
+          <t>0.009628948175406294 +/- 0.0013024692169024917</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.005673106409076945 +/- 0.001784138387953254</t>
+          <t>0.00634774609015637 +/- 0.002215776988592471</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.013615455381784691 +/- 0.0015406141290500172</t>
+          <t>-0.008126341613002196 +/- 0.0022293163285710725</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0004599816007360258 +/- 0.0006891200568612165</t>
+          <t>-0.0002453235203925486 +/- 0.00030045872343249243</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00042931616068694336 +/- 0.0006884374216695393</t>
+          <t>0.0007053051211284522 +/- 0.00047605564845936554</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.005059797608095651 +/- 0.001891587919446917</t>
+          <t>-0.01238883777982217 +/- 0.001930705457061901</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.00101195952161911 +/- 0.0011880632093106938</t>
+          <t>-0.0012266176019626429 +/- 0.0018903446804565947</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.0007666360012265727 +/- 0.0007026335012198415</t>
+          <t>0.0005213124808340353 +/- 0.0008347536086363836</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.0021159153633854345 +/- 0.00048389248200120775</t>
+          <t>-0.00021465808034351052 +/- 0.0007517725036572436</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.005274455688439183 +/- 0.0008866502480711936</t>
+          <t>0.002299908003679796 +/- 0.0019406644995150926</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.0072983747316773704 +/- 0.0016098625879676929</t>
+          <t>0.0015026065624041186 +/- 0.0012376839049745743</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.0022692425636308246 +/- 0.0004982544253073348</t>
+          <t>-0.001011959521619188 +/- 0.001062724529356849</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.003097209444955584 +/- 0.0015783022670908054</t>
+          <t>0.0022692425636307465 +/- 0.0010815818514902566</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.0022385771235816864 +/- 0.000845943834660147</t>
+          <t>-0.005519779208831699 +/- 0.0011876673861415062</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0011959521619134717 +/- 0.0016821328613189264</t>
+          <t>0.0015026065624041296 +/- 0.001021209801002575</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.008647654093836199 +/- 0.0021933829797298496</t>
+          <t>0.002606562404170454 +/- 0.0019260728301063897</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.005887764489420466 +/- 0.0020470186161642124</t>
+          <t>0.019993866911990156 +/- 0.0023626323562414195</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.002177246243483588 +/- 0.0007931626590847951</t>
+          <t>0.00030665440049061355 +/- 0.001483396089843328</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.002422569763876148 +/- 0.0015901738316423468</t>
+          <t>-0.0014106102422570376 +/- 0.0011892498883572637</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0029132168046611894 +/- 0.0008256922427375765</t>
+          <t>0.001441275682305998 +/- 0.0006439742410303523</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.0033425329653480884 +/- 0.0011179224859587948</t>
+          <t>0.0030665440049064243 +/- 0.0008887688896773661</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.0057651027292241475 +/- 0.0016330606508058179</t>
+          <t>-0.01143820913830118 +/- 0.001718633090365158</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.003342532965348033 +/- 0.0019847434682961672</t>
+          <t>-0.010886231217417996 +/- 0.0010732904017172655</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.006501073290401694 +/- 0.0014370284592284438</t>
+          <t>-0.003189205765102776 +/- 0.002080735412902484</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>9.199632014721404e-05 +/- 0.0004760556484593649</t>
+          <t>-0.0004906470407850638 +/- 0.0006009174468649327</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.00030665440049070235 +/- 0.0004750669544566008</t>
+          <t>0.000889297761422847 +/- 0.00046405231372038404</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0001371400170193112</t>
+          <t>0.0001533272002452901 +/- 0.0002057100255289544</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.013247470101195914 +/- 0.002594085983754263</t>
+          <t>-0.01631401410610246 +/- 0.0013282065518373362</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.004753143207605004 +/- 0.0018206596269607364</t>
+          <t>0.004170499846672749 +/- 0.0010988330491977364</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.00021465808034351052 +/- 0.0006439742410303571</t>
+          <t>-0.000275988960441631 +/- 0.0007185142296142169</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.004538485127261538 +/- 0.0005946249441786479</t>
+          <t>-0.00426249616682004 +/- 0.0012452585405855305</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.0008586323213738423 +/- 0.002240046901901224</t>
+          <t>-0.008831646734130661 +/- 0.001086785964223812</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.0012879484820607523 +/- 0.0006829517771027273</t>
+          <t>0.0002759889604415422 +/- 0.0006497890248517966</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.0016252683226004594 +/- 0.0010082356469042323</t>
+          <t>-0.006991720331186779 +/- 0.0013972138301005244</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.010702238577123569 +/- 0.0013468378568535914</t>
+          <t>-0.006623735050598023 +/- 0.0012509094176247292</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0.01094756209751615 +/- 0.0019202051155416493</t>
+          <t>0.005673106409076945 +/- 0.0008481641635043986</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.006838393130941411 +/- 0.0017076548043331275</t>
+          <t>0.0038638454461821015 +/- 0.0004790094864094822</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.0012266176019626429 +/- 0.00023753347722829324</t>
+          <t>0.00018399264029436146 +/- 0.0005167831814275634</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.004017172646427513 +/- 0.0009039805564540719</t>
+          <t>0.015118061944188865 +/- 0.0016229522995889964</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.007329040171726508 +/- 0.0010484710823231475</t>
+          <t>-0.0020545844832873805 +/- 0.0008234113205825153</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.0029745476847593323 +/- 0.000960469780028551</t>
+          <t>0.0042624961668199625 +/- 0.0014015817089268919</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.02002453235203928 +/- 0.0014516774460036443</t>
+          <t>0.02063784115302052 +/- 0.002274416637937892</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.0017479300827967336 +/- 0.0015878066195644982</t>
+          <t>-0.001042624961668248 +/- 0.0006746396810794051</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.004599816007359736 +/- 0.0014052670024397047</t>
+          <t>0.018368598589389717 +/- 0.001414936767256602</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>-0.00036798528058873403 +/- 0.00022947914055650615</t>
+          <t>-0.0001226617601962965 +/- 0.0002810534004879462</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0002453235203924931 +/- 0.00078541848971884</t>
+          <t>0.0029132168046610897 +/- 0.0006891200568612115</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0037718491260349983 +/- 0.0010627245293568506</t>
+          <t>0.0004906470407849972 +/- 0.0008136460693910821</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,52 +1711,52 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.002759889604415866 +/- 0.0005485600680772076</t>
+          <t>0.0010426249616681594 +/- 0.0008586323213737939</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.006378411530205519 +/- 0.0009281046274407468</t>
+          <t>-0.000490647040785075 +/- 0.0010902415721944947</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>-3.0665440049060245e-05 +/- 9.199632014718073e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0018092609628948652 +/- 0.00042158010073192585</t>
+          <t>0.0019012572830419793 +/- 0.0008971934276803354</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.004385157927016314 +/- 0.0011721260259807587</t>
+          <t>0.004845139527752196 +/- 0.0011039558417663328</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.0028825513646121292 +/- 0.0014655385642868644</t>
+          <t>0.009414290095062849 +/- 0.0011721260259807717</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.004017172646427513 +/- 0.0005562207036865101</t>
+          <t>0.003802514566083992 +/- 0.0007901931141812643</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0015639374425023612 +/- 0.00203157093836884</t>
+          <t>-0.004630481447408819 +/- 0.0010837532687563325</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.005611775528978869 +/- 0.0012270008600884729</t>
+          <t>0.01398344066237347 +/- 0.0014591079120969375</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.0018399264029438478 +/- 0.0012791569220861217</t>
+          <t>0.0010732904017172196 +/- 0.001577110195722007</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0032411537317870386 +/- 0.0015476674016857762</t>
+          <t>0.0031519476657746346 +/- 0.001198301616390732</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.005263157894736891 +/- 0.0014509512814458352</t>
+          <t>0.0021706809396372594 +/- 0.001382294296660051</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0023490930716621784 +/- 0.0014288449333016856</t>
+          <t>0.007820398453761545 +/- 0.0016611927116816417</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0024977698483496513 +/- 0.0011983016163907166</t>
+          <t>0.005857865001486795 +/- 0.0010131861455486802</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.004965804341361924 +/- 0.0010304920280204116</t>
+          <t>0.002081474873624767 +/- 0.001189414213499851</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0010704727921498347 +/- 0.0017551417857120037</t>
+          <t>2.2204460492503132e-17 +/- 0.001349605199870376</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.0006541778174249724 +/- 0.0003467708530981551</t>
+          <t>8.92060660125038e-05 +/- 0.00023224054938764588</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0005055010407373883 +/- 0.0009024080229255727</t>
+          <t>0.001694915254237339 +/- 0.0011443283618729596</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.011121022896223676 +/- 0.00302424790605795</t>
+          <t>0.008088016651799002 +/- 0.0036461899627640458</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.014510853404698232 +/- 0.0026854170454655027</t>
+          <t>0.0074338388343740845 +/- 0.0028521150896893884</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.0016057091882248574 +/- 0.001499794256665901</t>
+          <t>0.0027059173357121824 +/- 0.0008457604908312605</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.0034790365744871155 +/- 0.0014870650906987836</t>
+          <t>0.0022004162949747718 +/- 0.0011141834073859636</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.008920606601248826 +/- 0.001275504644039679</t>
+          <t>0.009069283377936365 +/- 0.000800648945455625</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0027653880463871074 +/- 0.001899574933533688</t>
+          <t>0.01332143919119837 +/- 0.0015324530153702214</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.0049658043413618345 +/- 0.0016289439101757005</t>
+          <t>0.0019327980969372715 +/- 0.0024744747215422486</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>5.9470710674947024e-05 +/- 0.0009753921776305067</t>
+          <t>-0.0011299435028248373 +/- 0.0009193948756312967</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.0027653880463872184 +/- 0.0010642598970070352</t>
+          <t>0.0019327980969373049 +/- 0.0010491988560438425</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0033303597977995315 +/- 0.0011879265153397437</t>
+          <t>0.0031222123104371335 +/- 0.0010741832808913614</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.003687184061849502 +/- 0.001304294510821348</t>
+          <t>0.002378828426999735 +/- 0.001316440298613058</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.0003865596193875165 +/- 0.00023224054938768849</t>
+          <t>0.0001784121320250076 +/- 0.0002378828426999685</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.008385370205174002 +/- 0.0023063597299631663</t>
+          <t>-0.009931608682723714 +/- 0.0017999103122713755</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.006066012488849193 +/- 0.001337760556550939</t>
+          <t>0.0035087719298245836 +/- 0.000909726942657042</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-5.551115123125783e-17 +/- 0.00097720349242671</t>
+          <t>-0.0020814748736247336 +/- 0.0010721234836348508</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0013083556348497782 +/- 0.0011759571771207485</t>
+          <t>-0.0007433838834373874 +/- 0.0010407374368123748</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.001100208147487325 +/- 0.0012619146698735048</t>
+          <t>-0.00017841213202495209 +/- 0.001505678132759104</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.00023788284269993243 +/- 0.00032025957818223596</t>
+          <t>-0.0003568242640499264 +/- 0.000511586397088463</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.005857865001486717 +/- 0.0018235799115625254</t>
+          <t>4.4408920985006264e-17 +/- 0.0018038359664707992</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.0006541778174248725 +/- 0.0009097269426570746</t>
+          <t>-0.0008920606601248715 +/- 0.0011046194243834022</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0033006244424620525 +/- 0.0009538516165533855</t>
+          <t>0.004638715432649454 +/- 0.0010487774063959925</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.007255426702349044 +/- 0.0012974977240125536</t>
+          <t>0.0019625334522747504 +/- 0.0008740373747665289</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.00014867677668742863 +/- 0.0003819575551193905</t>
+          <t>-0.00038655961938742766 +/- 0.00035308778135703845</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.00011894142135002728 +/- 0.00027252903330098353</t>
+          <t>-0.00017841213202495209 +/- 0.0005011091152647107</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.004103479036574454 +/- 0.0014185977331997153</t>
+          <t>0.0018138566755872998 +/- 0.0013525501534991625</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.0057686589354743354 +/- 0.0012837962024931707</t>
+          <t>-0.003895331549212011 +/- 0.001720801224648246</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.000981266726137331 +/- 0.0007759731400951349</t>
+          <t>0.0006839131727624292 +/- 0.000532752687099867</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-8.920606601253711e-05 +/- 0.0006101184813762688</t>
+          <t>0.0013678263455248474 +/- 0.0006405191563644925</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.003151947665774557 +/- 0.0018768639712232673</t>
+          <t>0.006839131727624159 +/- 0.0014445385431449463</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0063038953315491695 +/- 0.0011030173649117625</t>
+          <t>0.0016651798988998267 +/- 0.0008110723578344437</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.0009515313707998407 +/- 0.0003944840666494552</t>
+          <t>-0.00047576568539990926 +/- 0.00056731442249002</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.0021409455842996694 +/- 0.0008999551561356922</t>
+          <t>-0.002824858757062121 +/- 0.000874543037160419</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.004341361879274408 +/- 0.0012056577420584656</t>
+          <t>0.006868867082961661 +/- 0.0008028545941123993</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.0004162949747249844 +/- 0.0018674181942441217</t>
+          <t>0.005292893250074382 +/- 0.00107047279214986</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.004519774011299471 +/- 0.0008389376140152009</t>
+          <t>-0.00395480225988698 +/- 0.0014325530146233557</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.002200416294974683 +/- 0.0016566622988027522</t>
+          <t>0.005501040737436858 +/- 0.0018958475324763614</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0019327980969372272 +/- 0.0009884490121079314</t>
+          <t>0.00223015165031224 +/- 0.00104073743681237</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.002378828426999646 +/- 0.0011668996057299164</t>
+          <t>-0.0011299435028248484 +/- 0.0015033273457941724</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.00020814748736244226 +/- 0.00026761819803746453</t>
+          <t>-0.0010704727921498347 +/- 0.00023788284269998794</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0009217960154623506 +/- 0.001100208147487357</t>
+          <t>0.0029735355337496493 +/- 0.0010884927277860705</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.0026761819803747255 +/- 0.001356140856496146</t>
+          <t>-0.0052334225393993235 +/- 0.0019777923459192276</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.005619982158786852 +/- 0.001465503601588084</t>
+          <t>-0.012518584597085903 +/- 0.0012577035969406154</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0005352363960748896 +/- 0.0017430093237886073</t>
+          <t>-0.006006541778174224 +/- 0.0011953464907666865</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.00041629497472499554 +/- 0.0004644810987753187</t>
+          <t>-0.00038655961938742766 +/- 0.0007410012366563727</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0013083556348498892 +/- 0.0004644810987752917</t>
+          <t>-0.0006839131727623737 +/- 0.0005158891338952738</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-0.0013380909901873795 +/- 0.0004654319310882631</t>
+          <t>-0.0017841213202497651 +/- 0.0006093934443032868</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.005828129646149327 +/- 0.0012629652442221273</t>
+          <t>-0.010258697591436194 +/- 0.002214236002513394</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.004281891168599505 +/- 0.0019141810216391558</t>
+          <t>-0.003062741599762109 +/- 0.001568099538915861</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.0003761257996037515</t>
+          <t>0.001040737436812389 +/- 0.0005193056555626859</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-0.0005352363960749673 +/- 0.0004940008244376059</t>
+          <t>0.0027059173357121937 +/- 0.0011853185505795248</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.003003270889087173 +/- 0.0008245866561916239</t>
+          <t>-0.007612250966399026 +/- 0.0015462384775497995</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0005055010407373995 +/- 0.0005649717514124231</t>
+          <t>-0.0007136485280998861 +/- 0.0005011091152647252</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.0045197740112993936 +/- 0.0012810383127289716</t>
+          <t>0.001189414213499862 +/- 0.0012685536133036812</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.004906333630686932 +/- 0.0011381301938153299</t>
+          <t>-0.014600059470710646 +/- 0.0013525501534991742</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.0048171275646743394 +/- 0.0011577711765644824</t>
+          <t>0.007344632768361603 +/- 0.001080748251286725</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.0029438001784120814 +/- 0.0012923766763069172</t>
+          <t>0.014986619090098153 +/- 0.001591327762148041</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.00018806289980186257</t>
+          <t>-0.00011894142134997177 +/- 0.00019724203332472008</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0014867677668747525 +/- 0.000564188699405576</t>
+          <t>0.015343443354148122 +/- 0.0014334785362109964</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0027059173357121156 +/- 0.0011318980856779277</t>
+          <t>-0.0011894142134998287 +/- 0.0011894142134998536</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.0010407374368123002 +/- 0.0005834498028649384</t>
+          <t>-0.0010110020814748544 +/- 0.0003807983489404201</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.0029140648230745803 +/- 0.0008389376140152174</t>
+          <t>0.018227772821885237 +/- 0.0018902426494573636</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.0012191495688373855 +/- 0.0008765627697284356</t>
+          <t>0.004252155813261993 +/- 0.0006787221058884026</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-0.0003865596193875054 +/- 0.0007759731400951546</t>
+          <t>0.0036871840618495576 +/- 0.0013574442117767766</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-0.00011894142135000507 +/- 0.00035682426404996895</t>
+          <t>0.000386559619387461 +/- 0.00023224054938763872</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>8.920606601244829e-05 +/- 0.0006521472554106846</t>
+          <t>0.0012488849241748534 +/- 0.0006208924477496726</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.0005055010407373883 +/- 0.0006521472554106792</t>
+          <t>0.00023788284269998794 +/- 0.0008699814949942305</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.0004460303300625079 +/- 0.0006548532722434125</t>
+          <t>0.0001784121320249854 +/- 0.0005515086824558708</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.001784121320249721 +/- 0.0013231397836031486</t>
+          <t>0.003835860838537042 +/- 0.0010675779405897483</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00038655961938741654 +/- 0.00019039917447021004</t>
+          <t>0.00014867677668750634 +/- 0.0004460303300624376</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.0007136485280999638 +/- 0.0008110723578344404</t>
+          <t>0.005055010407374394 +/- 0.000763915110238781</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.003360095153137044 +/- 0.0008520100375792133</t>
+          <t>0.006066012488849271 +/- 0.0014997942566659097</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.00023788284269992132 +/- 0.00029134579158884876</t>
+          <t>-2.9735355337467962e-05 +/- 0.00020814748736246606</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.00029735355337500157 +/- 0.0010638444139160447</t>
+          <t>-0.0021409455842997136 +/- 0.0011110045609437722</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.006333630686886671 +/- 0.001174828799591947</t>
+          <t>0.005857865001486795 +/- 0.0016451473319801487</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.0002973535533749239 +/- 0.0006237340756289811</t>
+          <t>0.001665179898899838 +/- 0.0006935417061963036</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.004564315352697146 +/- 0.0017693908188025646</t>
+          <t>0.002815649081209237 +/- 0.0017596831782806573</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.009839952578541866 +/- 0.0014201717309675042</t>
+          <t>-0.0027267338470657876 +/- 0.001146359194179825</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.002726733847065821 +/- 0.0021032833431192006</t>
+          <t>0.0013633669235328938 +/- 0.001724130358298629</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.015174866627148842 +/- 0.001915292758909716</t>
+          <t>0.0013633669235328938 +/- 0.0015694371422493988</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.010551274451689463 +/- 0.001602668148736897</t>
+          <t>0.003082394783639586 +/- 0.0018279957255612589</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.014997036158861943 +/- 0.002368107214634038</t>
+          <t>-0.002430349733254289 +/- 0.00219324244220509</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.00047421458209839784 +/- 0.0003300393813177239</t>
+          <t>-0.00011855364552459946 +/- 0.0003022536759687473</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.005453467694131664 +/- 0.001410240338277483</t>
+          <t>0.0023414344991108393 +/- 0.0009690446191032458</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.013900414937759287 +/- 0.0025407916028627993</t>
+          <t>0.029253112033195028 +/- 0.004319588747971332</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.029134558387670383 +/- 0.0018980157257363036</t>
+          <t>0.020361588618850034 +/- 0.0037631446363521146</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0010669828097213951 +/- 0.0013594955472649287</t>
+          <t>-0.0010669828097213951 +/- 0.000957646379454858</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.0133669235328987 +/- 0.001013356312820314</t>
+          <t>-0.00880260818020151 +/- 0.0011859068775188196</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.0020746887966805127 +/- 0.0019299135265085823</t>
+          <t>-0.00011855364552459946 +/- 0.0019489368373175507</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.01114404267931235 +/- 0.001823183935889703</t>
+          <t>0.005749851807943074 +/- 0.00230036845428953</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.010106698280972215 +/- 0.0023690343934075274</t>
+          <t>-0.006075874333135722 +/- 0.0014105517527315651</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.012685240071132253 +/- 0.0016597510373443924</t>
+          <t>-0.0027563722584469375 +/- 0.0015403422003777399</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.007172495554238367 +/- 0.0017674038548756033</t>
+          <t>-0.0005038529934795477 +/- 0.0014093056820354119</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.006164789567279283 +/- 0.0012490401603856196</t>
+          <t>0.001956135151155891 +/- 0.0010537278503041563</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.004149377593361025 +/- 0.0022727077074903537</t>
+          <t>-0.005423829282750425 +/- 0.001305773015525229</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.00038529934795494825 +/- 0.00013582026363235993</t>
+          <t>0.00020746887966804906 +/- 0.00013582026363235993</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.008150563129816213 +/- 0.002484151543307669</t>
+          <t>0.011558980438648447 +/- 0.001865101686135414</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.008180201541197474 +/- 0.0015182274421891705</t>
+          <t>-0.0014522821576763434 +/- 0.0015080680774402497</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0032602252519265294 +/- 0.001155518001755701</t>
+          <t>0.0013633669235328938 +/- 0.0008084280792522708</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0008595139300533461 +/- 0.0008325175995962115</t>
+          <t>0.00011855364552459946 +/- 0.0011105509185059352</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.000652045050385297 +/- 0.0012490401603856196</t>
+          <t>0.0025489033787788884 +/- 0.001441048699602036</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0003260225251926485 +/- 0.0005038529934795477</t>
+          <t>0.0012151748666271445 +/- 0.0003852993479549482</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.007824540604623675 +/- 0.0024411689723739098</t>
+          <t>0.0036455245998814334 +/- 0.002226040039196839</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.019590989922940172 +/- 0.0013284490119155241</t>
+          <t>-0.0034084173088322345 +/- 0.0017942870026870488</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.008476585655008972 +/- 0.0008610455866232304</t>
+          <t>-0.002845287492590387 +/- 0.0012234598364285845</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.010818020154119812 +/- 0.0010288414319922774</t>
+          <t>-0.0004149377593360981 +/- 0.0015638299891254145</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-0.000444576170717248 +/- 0.0004639145181534817</t>
+          <t>0.0013930053349140437 +/- 0.0004201970029270236</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.0015708358032009428 +/- 0.0005142072191137348</t>
+          <t>0.00020746887966804906 +/- 0.00047882318972742905</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.007202133965619528 +/- 0.0012366713719635443</t>
+          <t>-0.0029045643153526868 +/- 0.0015727918389355725</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.012477771191464204 +/- 0.0013803356280017755</t>
+          <t>-0.002667457024303488 +/- 0.001351719531830627</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-0.0008298755186721962 +/- 0.00045531391510779965</t>
+          <t>0.0015115589804386431 +/- 0.0005693352908209389</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.0010077059869590954 +/- 0.00048156718462572207</t>
+          <t>0.000652045050385297 +/- 0.00047421458209839784</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.00652045050385297 +/- 0.0017979550549025545</t>
+          <t>0.0034380557202133843 +/- 0.00119439488320153</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.007765263781861376 +/- 0.0013174932288614577</t>
+          <t>-0.003112033195020736 +/- 0.0015864165608859026</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.0008298755186721962 +/- 0.0007235658337720011</t>
+          <t>0.001541197391819793 +/- 0.0005747101194328763</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.00047421458209839784 +/- 0.001272727359429983</t>
+          <t>0.002637818612922338 +/- 0.0012813258044586371</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.006757557794902269 +/- 0.002031042287968216</t>
+          <t>-0.0022525192649673897 +/- 0.0009391214889006997</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.0012151748666271445 +/- 0.001096621221102545</t>
+          <t>-0.001096621221102545 +/- 0.0013191590447105992</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.0012744516893894553 +/- 0.0016820940869784</t>
+          <t>-0.002608180201541188 +/- 0.00140149263989767</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.003556609365738028 +/- 0.001222023006999938</t>
+          <t>0.012803793716656752 +/- 0.0021364340593882933</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.003586247777119189 +/- 0.0013930053349140944</t>
+          <t>0.001096621221102545 +/- 0.0011558980438648447</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0037937166567871827 +/- 0.0014747901961617883</t>
+          <t>0.0001778304682868992 +/- 0.0011795938792016792</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.0001778304682868992 +/- 0.0005167633602300721</t>
+          <t>-0.00020746887966804906 +/- 0.00047882318972742905</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>-0.0075874333135744765 +/- 0.0007751450403451082</t>
+          <t>-0.0005334914048606976 +/- 0.0005747101194328763</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.0021339656194428237 +/- 0.0023254351210353617</t>
+          <t>-0.003112033195020736 +/- 0.0010288414319922774</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.016360403082394837 +/- 0.0024325174307863805</t>
+          <t>-0.004831061055127428 +/- 0.0016073203157031656</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.0046828689982217455 +/- 0.00212406317334549</t>
+          <t>-0.007854179016004714 +/- 0.0017596831782806573</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.0013633669235328938 +/- 0.0007637284366760569</t>
+          <t>-0.0005334914048606976 +/- 0.0006045073519374946</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.00014819205690574933 +/- 0.00048247838162713836</t>
+          <t>-0.0005038529934795477 +/- 0.0011634728172134235</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.00014819205690574933 +/- 0.0003037033422038993</t>
+          <t>2.9638411381149865e-05 +/- 0.0002461951352376421</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.018850029638411425 +/- 0.0017087771553526406</t>
+          <t>-0.007172495554238267 +/- 0.001691208371984239</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.009810314167160716 +/- 0.0015196732357195288</t>
+          <t>-0.007468879668049766 +/- 0.0009539701801678141</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.0032602252519265186 +/- 0.0006758597659153574</t>
+          <t>-0.0015708358032009428 +/- 0.0007019987719221677</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.003645524599881489 +/- 0.0009834416136951878</t>
+          <t>-0.00038529934795494825 +/- 0.0008797167800625832</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.00029638411381150976 +/- 0.002116605936141938</t>
+          <t>-0.008328393598103112 +/- 0.0022157562171387793</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.0013930053349140437 +/- 0.0008994659695016873</t>
+          <t>-0.00038529934795494825 +/- 0.00047882318972742905</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.006757557794902269 +/- 0.0018067279969328155</t>
+          <t>-0.0009780675755779455 +/- 0.0011014169636077047</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.010077059869591065 +/- 0.001763423210509006</t>
+          <t>0.0003260225251926485 +/- 0.001838776214492714</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.0005927682276229973 +/- 0.001408993992176013</t>
+          <t>0.0009187907528156458 +/- 0.0015311904390147534</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.029934795494961475 +/- 0.001464029524034194</t>
+          <t>-0.004090100770598681 +/- 0.0008362024884212112</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-5.927682276229973e-05 +/- 0.00011855364552459945</t>
+          <t>0.0001778304682868992 +/- 0.0001451979693410296</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.018672199170124526 +/- 0.0008170746148245509</t>
+          <t>-0.003467694131594534 +/- 0.0009923336717713779</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.0012151748666271445 +/- 0.0009320797387976485</t>
+          <t>-0.0004149377593360981 +/- 0.0008192219893944993</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.005364552459988204 +/- 0.001508068077440292</t>
+          <t>-0.0011262596324836949 +/- 0.0006045073519374946</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.027771191464137535 +/- 0.001148273303367543</t>
+          <t>-0.004564315352697079 +/- 0.0014226437462951935</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.016330764671013687 +/- 0.0017203049034891997</t>
+          <t>-0.0017190278601066922 +/- 0.001304090100770594</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.03135743924125668 +/- 0.0019426164325043371</t>
+          <t>-0.003052756372258436 +/- 0.001093412373781663</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-8.89152341434496e-05 +/- 0.00039874404407450097</t>
+          <t>-0.00029638411381149865 +/- 0.0001874497723869809</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.0032602252519265073 +/- 0.0007259898467051753</t>
+          <t>0.002371072910491989 +/- 0.0009558100472197417</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.007231772377000678 +/- 0.0012090147038749891</t>
+          <t>0.0009187907528156458 +/- 0.000584560845385772</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.002904564315352698 +/- 0.000589796939600863</t>
+          <t>-0.0016597510373443924 +/- 0.00046296678576802767</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.010047421458209915 +/- 0.0013866849514273319</t>
+          <t>-0.0014226437462951935 +/- 0.0008466423744567664</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.003645524599881489 +/- 0.0011634728172134673</t>
+          <t>0.0003260225251926485 +/- 0.00027960821375389955</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.019264967397747523 +/- 0.001345205182917626</t>
+          <t>0.0009187907528156458 +/- 0.0009507418454265194</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-0.011499703615886259 +/- 0.001146359194179825</t>
+          <t>0.0015115589804386431 +/- 0.0018766053489361798</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-0.003438055720213451 +/- 0.0010111868470203083</t>
+          <t>0.00023710729104919892 +/- 0.0006732552869946951</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.014878482513337343 +/- 0.0013040901007705943</t>
+          <t>-0.002430349733254289 +/- 0.0010335267204601441</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.016567871962062886 +/- 0.001604037833756344</t>
+          <t>-0.004090100770598681 +/- 0.0011309296993680408</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.007824540604623675 +/- 0.0015297555305944155</t>
+          <t>0.002874925903971537 +/- 0.0007503846414447017</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.00704518430439951 +/- 0.0010128849606064658</t>
+          <t>0.004042806183115399 +/- 0.0012342770209290517</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0033590963139119912 +/- 0.0022523598976830843</t>
+          <t>0.0036563614744352323 +/- 0.0012823813680215874</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0014268727705112783 +/- 0.0010280390288817127</t>
+          <t>0.0016646848989298802 +/- 0.0013173911894269008</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.0022592152199762626 +/- 0.0011905460401011125</t>
+          <t>-0.003923900118906021 +/- 0.0012314099391919102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0036860879904874965 +/- 0.0016454640312839458</t>
+          <t>0.0041914387633769645 +/- 0.0005391901648994552</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0021997621878715678 +/- 0.0013635368538858052</t>
+          <t>-0.004726516052318619 +/- 0.0012643383066668604</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00023781212841854636 +/- 0.0004566674047484234</t>
+          <t>0.0008323424494649512 +/- 0.00043688877695301936</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.002645659928656341 +/- 0.0014830522810066972</t>
+          <t>0.0006837098692033527 +/- 0.0017386835690713308</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.01923305588585015 +/- 0.004535705290206663</t>
+          <t>0.016379310344827636 +/- 0.0022263156175211336</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.03849583828775266 +/- 0.004017481181593656</t>
+          <t>0.022057074910820474 +/- 0.0020543582096517236</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.004726516052318686 +/- 0.0021206072327005785</t>
+          <t>0.0008917954815696016 +/- 0.001394297193764418</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.008531510107015439 +/- 0.0019036578652301354</t>
+          <t>0.005737217598097555 +/- 0.0010966627078297612</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.005053507728894157 +/- 0.0012681765165102005</t>
+          <t>0.00029726516052323013 +/- 0.0011513030161139815</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.019292508917954854 +/- 0.00174578440666183</t>
+          <t>-0.01765755053507727 +/- 0.0024375743162901296</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-0.003953626634958396 +/- 0.003245640073164757</t>
+          <t>0.004102259215220017 +/- 0.0013079667063020388</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.0007431629013079921 +/- 0.0013244155416138582</t>
+          <t>-0.0011296076099880815 +/- 0.0011497669206785729</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.0006837098692033083 +/- 0.0013429675384157643</t>
+          <t>0.006212841854934659 +/- 0.001614289415265799</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.004934601664684924 +/- 0.0012834145746089532</t>
+          <t>-0.002705112960760947 +/- 0.001075508472956332</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.007788347205707491 +/- 0.0015145944355359126</t>
+          <t>0.0004161712247324978 +/- 0.0014144324914828034</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.0002080856123662378 +/- 0.00046147962830738864</t>
+          <t>0.0005053507728894346 +/- 0.00023217151236346376</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0003864447086801337 +/- 0.0024622816159189974</t>
+          <t>-0.0041914387633768865 +/- 0.0015642475763285092</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.00475624256837095 +/- 0.0008818309734953154</t>
+          <t>0.00041617122473250887 +/- 0.0013106663308590173</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0025862068965516794 +/- 0.0014565992865636249</t>
+          <t>0.00011890606420930094 +/- 0.0007774492764935737</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.972651605229748e-05 +/- 0.0011078861565745732</t>
+          <t>-0.0005350772889416878 +/- 0.001078380329798867</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.00023781212841854636 +/- 0.0010783803297988886</t>
+          <t>0.0013971462544590252 +/- 0.000752615273553662</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.00026753864447085494 +/- 0.000586298541121151</t>
+          <t>0.0010701545778835087 +/- 0.0004829987160901449</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.0037158145065398496 +/- 0.002682807780587031</t>
+          <t>-0.00047562425683704833 +/- 0.002181205270849474</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.000802615933412587 +/- 0.001516052318668262</t>
+          <t>-0.004667063020214001 +/- 0.0012474515611389562</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.0035374554102259427 +/- 0.0014222204178246673</t>
+          <t>-0.00903686087990484 +/- 0.0007425681329843566</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0019322235434006795 +/- 0.0009138184392948662</t>
+          <t>-0.0007728894173602341 +/- 0.0019182242336387256</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0006837098692033083 +/- 0.0005648038049940285</t>
+          <t>0.00032699167657551653 +/- 0.0004086720298712244</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.000564803804994074 +/- 0.00046907651123840786</t>
+          <t>0.000564803804994074 +/- 0.00046907651123840786</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,272 +2826,272 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.0017835909631391366 +/- 0.0012611892648987186</t>
+          <t>-0.0024375743162900697 +/- 0.001273738720905382</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.004994054696789552 +/- 0.001496989097742451</t>
+          <t>-0.0018430439952437205 +/- 0.0016805343668373925</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>5.945303210463937e-05 +/- 0.0004161712247324756</t>
+          <t>-0.0013971462544589252 +/- 0.0007526152735536459</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.000891795481569535 +/- 0.0007159093090839482</t>
+          <t>0.0007134363852556724 +/- 0.0006673586302212966</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0014863258026159066 +/- 0.0016443896178287099</t>
+          <t>-0.0016349583828774938 +/- 0.000979171765279465</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.003299643281807396 +/- 0.0010421253354909758</t>
+          <t>-0.0035969084423305266 +/- 0.0007915295455228335</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.0010404280618311224 +/- 0.0010982730797806741</t>
+          <t>-0.0010107015457787693 +/- 0.00044490575348084656</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.00014863258026157622 +/- 0.0011983141718636449</t>
+          <t>0.0018133174791914897 +/- 0.0008661594699365947</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.004785969084423325 +/- 0.0016414313546110142</t>
+          <t>-0.0014863258026158843 +/- 0.0012470973224377468</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.006420927467300852 +/- 0.00129711202314338</t>
+          <t>-0.004577883472057042 +/- 0.001081653115259233</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.003745541022592147 +/- 0.0015110897773054648</t>
+          <t>0.002140309155766973 +/- 0.0009286860494538118</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.004904875148632604 +/- 0.001923055171181421</t>
+          <t>-0.0063614744351961575 +/- 0.0009512485136741924</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0010404280618311224 +/- 0.0010982730797806772</t>
+          <t>-0.0004161712247324201 +/- 0.0010651886365736411</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.0010107015457788582 +/- 0.0010978707082413607</t>
+          <t>0.0005648038049940851 +/- 0.0011997881135916077</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.001961950059452988 +/- 0.0005182995176624045</t>
+          <t>-0.00011890606420925654 +/- 0.0005671457796771268</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.0006837098692033305 +/- 0.0009952835340536915</t>
+          <t>0.003686087990487552 +/- 0.0008636051751684904</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.006896551724137901 +/- 0.0016107273702906033</t>
+          <t>0.013674197384066644 +/- 0.0018941179931122449</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.005499405469678986 +/- 0.0014395124866591112</t>
+          <t>-0.0047562425683709605 +/- 0.001572979376376104</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0010701545778834642 +/- 0.0014392055216302284</t>
+          <t>-0.004102259215219927 +/- 0.001102689476277727</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.00047562425683710384 +/- 0.000356718192627814</t>
+          <t>0.00035671819262784733 +/- 0.0005448960398282799</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.0011593341260404233 +/- 0.0006011815819309104</t>
+          <t>0.00023781212841855748 +/- 0.00037128406649218854</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.0007431629013079921 +/- 0.00027406493630479197</t>
+          <t>-0.0005945303210463271 +/- 0.00035172888127819185</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.0001486325802615873 +/- 0.0016723642305630454</t>
+          <t>2.972651605235299e-05 +/- 0.0012502818575988782</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.012752675386444678 +/- 0.0019239739744690192</t>
+          <t>0.007609988109393617 +/- 0.0016238406996132923</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.00023781212841855748 +/- 0.00011890606420927873</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0.000564803804994074 +/- 0.00033762832020216814</t>
+          <t>0.00032699167657552765 +/- 0.0007090880167584262</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.000802615933412587 +/- 0.0016230242205373087</t>
+          <t>0.004102259215220017 +/- 0.001231409939191905</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0.004458977407847775 +/- 0.0007159093090839482</t>
+          <t>0.003329369797859727 +/- 0.0018072157138609556</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0007401842804987386</t>
+          <t>-0.0008917954815694906 +/- 0.00046052120644559204</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.008115338882282986 +/- 0.001226016089613627</t>
+          <t>-0.00014863258026155403 +/- 0.0013703246815239167</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.007193816884661142 +/- 0.0014851362659687097</t>
+          <t>-0.007193816884661075 +/- 0.0017272103503369702</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.001278240190249713 +/- 0.0011968384149344462</t>
+          <t>-0.003359096313911969 +/- 0.0016284596819027644</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.0021700356718192372 +/- 0.0014259435142938706</t>
+          <t>-0.0021105826397145866 +/- 0.0012851347396680987</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>0.00011890606420927874 +/- 0.0003567181926278362</t>
+          <t>0.00026753864447087716 +/- 0.00028043939155936165</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.0012782401902497464 +/- 0.0013946140434886972</t>
+          <t>0.0034780023781213255 +/- 0.0013028898335797378</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.008234244946492253 +/- 0.0013028898335797378</t>
+          <t>0.001605231866825263 +/- 0.0008937750522219632</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.00047562425683708167 +/- 0.0009324843722567212</t>
+          <t>0.0018133174791914897 +/- 0.0006837098692033291</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.010434007134363843 +/- 0.001704809864321002</t>
+          <t>-0.0007728894173602563 +/- 0.0016878798533386979</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.001218787158145085 +/- 0.0010336110969508755</t>
+          <t>0.0033590963139120467 +/- 0.0009682816572474522</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.00023781212841852417 +/- 0.0016646848989298555</t>
+          <t>0.006837098692033338 +/- 0.0011964691912900178</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.00029726516052319685 +/- 0.00018800699525377452</t>
+          <t>0.00023781212841855748 +/- 0.00022245287674043217</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.000356718192627814 +/- 0.0006207078780564939</t>
+          <t>0.0008917954815696016 +/- 0.0008407928432658207</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.0004161712247324867 +/- 0.0009877079504064421</t>
+          <t>0.0015755053507729322 +/- 0.0007526152735536414</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-0.00014863258026159842 +/- 0.00014863258026159842</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.0002080856123662489 +/- 0.0008620689655172491</t>
+          <t>0.0009809750297265496 +/- 0.00044191643125205153</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.0006539833531509998 +/- 0.0013993581802544184</t>
+          <t>-0.0008323424494648957 +/- 0.0012023631638618663</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-0.0005350772889417543 +/- 0.00011890606420927873</t>
+          <t>-0.0017241379310344307 +/- 0.00022245287674043217</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.00023781212841853528 +/- 0.000648556011571673</t>
+          <t>0.00044589774078479527 +/- 0.00040432433141307695</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.004756242568370972 +/- 0.0011890606420927458</t>
+          <t>-0.0032401902497026904 +/- 0.0010755084729563331</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.0005648038049940185 +/- 0.001271308250912189</t>
+          <t>0.0022889417360285936 +/- 0.0009118823811045167</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>-0.0005053507728894346 +/- 0.0007642663574425018</t>
+          <t>-0.0012187871581450071 +/- 0.0007335887443075655</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0001486325802615873 +/- 0.001714114535474264</t>
+          <t>-0.003834720570749073 +/- 0.0007455372297255707</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.000891795481569535 +/- 0.0011964691912900124</t>
+          <t>0.0036266349583829348 +/- 0.0012385651995243476</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.0018727705112961067 +/- 0.0010556052856459347</t>
+          <t>0.0008323424494649512 +/- 0.0007134363852556724</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.0061743341404358 +/- 0.0012783724020546659</t>
+          <t>-0.006355932203389781 +/- 0.001560992367824181</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.006234866828087137 +/- 0.0011892786140671034</t>
+          <t>-0.0012711864406779183 +/- 0.0016399778673298084</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.004993946731234833 +/- 0.0016591368127924614</t>
+          <t>-0.005326876513317136 +/- 0.0015325652422726519</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0018462469733656396 +/- 0.0016098167248150223</t>
+          <t>0.0004842615012107032 +/- 0.001041443736930087</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.020127118644067778 +/- 0.0016029736896931526</t>
+          <t>-0.0035108958837771985 +/- 0.0007680737009957273</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.019733656174334126 +/- 0.002763368573974178</t>
+          <t>-0.005599273607748123 +/- 0.001642489534045421</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.0266343825691155e-05 +/- 0.0003159899064440222</t>
+          <t>-0.00036319612590793857 +/- 0.00029654839501006176</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.01062348668280868 +/- 0.0016984246787649147</t>
+          <t>-0.005296610169491489 +/- 0.002008782506785126</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.005962469733656195 +/- 0.0027004974611010133</t>
+          <t>0.0077481840193704965 +/- 0.002360774818401943</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.005175544794188891 +/- 0.001725181598062952</t>
+          <t>0.02112590799031482 +/- 0.002819160053800239</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.004721549636803846 +/- 0.0011737723625705296</t>
+          <t>-0.003783292978208186 +/- 0.0019010059016273863</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.014981840193704576 +/- 0.0016312969707278184</t>
+          <t>-0.009079903147699731 +/- 0.0018159806295399575</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.01719128329297819 +/- 0.0013988159816333502</t>
+          <t>-0.007475786924939443 +/- 0.001816232831559019</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.006567796610169496 +/- 0.002417710706239903</t>
+          <t>0.0031779661016949623 +/- 0.0025403903835040332</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.0005447941888619523 +/- 0.0023002421307506096</t>
+          <t>0.00039346246973369635 +/- 0.0017016577235920997</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.003541162227602879 +/- 0.001091688183829983</t>
+          <t>-0.0016041162227602435 +/- 0.0010832645380250273</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.011410411622276007 +/- 0.0012701050398521384</t>
+          <t>-0.0034503631961258717 +/- 0.0007680737009957421</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.004176755447941849 +/- 0.0012241978460143248</t>
+          <t>-0.0069612590799031145 +/- 0.0017544039644297172</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.00550847457627115 +/- 0.0010979635077007946</t>
+          <t>-0.003995157384987846 +/- 0.0013656796819223312</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.00033292978208226964 +/- 0.0002855321165876611</t>
+          <t>0.00015133171912835587 +/- 0.00020303280667370563</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.0023910411622275808 +/- 0.0021927960879757906</t>
+          <t>0.000938256658595682 +/- 0.0021292109366781503</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.003389830508474523 +/- 0.0011469307095336877</t>
+          <t>-0.005447941888619812 +/- 0.001255232527441137</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.0006658595641646836 +/- 0.0008211053248335557</t>
+          <t>0.00208837772397098 +/- 0.0009802745000424644</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0013922518159806608 +/- 0.0007799091238937749</t>
+          <t>0.00015133171912836695 +/- 0.001361985472154957</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0003631961259079719 +/- 0.0019605490000849466</t>
+          <t>0.0019370460048426575 +/- 0.0013750383403874854</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.00027239709443103164 +/- 0.0006828398409611486</t>
+          <t>0.0004539951573850454 +/- 0.00043334809513549997</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>9.079903147701796e-05 +/- 0.002140367700755104</t>
+          <t>0.0016343825665860012 +/- 0.0010929461310694808</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.008777239709443075 +/- 0.00327660256724561</t>
+          <t>-0.009987893462469699 +/- 0.0023638770205528553</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.003087167070217911 +/- 0.0010019942710197726</t>
+          <t>0.00018159806295404702 +/- 0.0011659419058267675</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.003420096852300214 +/- 0.001900041902629489</t>
+          <t>0.002542372881355992 +/- 0.0013344677775453159</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.001119854721549607 +/- 0.0005907754629522668</t>
+          <t>0.00012106537530269801 +/- 0.0003875983194571922</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.0016646489104115924 +/- 0.0006526591601951775</t>
+          <t>0.00027239709443103164 +/- 0.000496404947544114</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.0035714285714285587 +/- 0.001462838495592573</t>
+          <t>0.0023607748184020006 +/- 0.0012091394888279691</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.007052058111380122 +/- 0.0017546650170261224</t>
+          <t>-0.00723365617433408 +/- 0.0017928817457167148</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.0009382566585956709 +/- 0.0005145278450363238</t>
+          <t>5.551115123125783e-17 +/- 0.0007162324192614575</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.00021186440677961604 +/- 0.0004071920111099729</t>
+          <t>-0.0006355932203389259 +/- 0.0005145278450363205</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.002027845036319598 +/- 0.0011958078852989395</t>
+          <t>-9.079903147694024e-05 +/- 0.0012628720366237912</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>0.00015133171912837807 +/- 0.0015857369125217575</t>
+          <t>-0.005901937046004791 +/- 0.0014593902483342855</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.0021186440677965824 +/- 0.0008343855176810109</t>
+          <t>0.00099878934624702 +/- 0.0008013439645807174</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.003813559322033877 +/- 0.0008255557927957577</t>
+          <t>-0.0006658595641645948 +/- 0.0015361474019914914</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.00027239709443097613 +/- 0.0009125189728620475</t>
+          <t>-0.003995157384987846 +/- 0.0013856565547529962</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0016646489104116592 +/- 0.001126379786073146</t>
+          <t>-0.00015133171912827813 +/- 0.0015857369125217736</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.002905569007263897 +/- 0.0009100058340419236</t>
+          <t>-0.005901937046004791 +/- 0.0013279304460339118</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.00599273607748182 +/- 0.0014565628832343901</t>
+          <t>-0.006628329297820779 +/- 0.0014353396732904723</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.004176755447941849 +/- 0.0009928098950881645</t>
+          <t>-0.0034503631961258496 +/- 0.0008896451850302057</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.0013619854721550028 +/- 0.0012200753251057038</t>
+          <t>0.0003026634382566895 +/- 0.0011079300979251357</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.0006658595641646836 +/- 0.0007984809902102124</t>
+          <t>0.0008474576271186973 +/- 0.00042372881355932885</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0.0026331719128329435 +/- 0.0014518383723016134</t>
+          <t>-0.0017251815980629081 +/- 0.0017441924375573828</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.008050847457627108 +/- 0.0017967096948735912</t>
+          <t>-0.002723970944309884 +/- 0.001537339600387462</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.006749394673123454 +/- 0.0018659882132927902</t>
+          <t>-0.0023002421307505736 +/- 0.0019948253091142893</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.002269975786924927 +/- 0.0019858504482232744</t>
+          <t>0.0027845036319613216 +/- 0.0013589554673513206</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.0008777239709442996 +/- 0.0005813974791857936</t>
+          <t>0.00021186440677968267 +/- 0.00023638770205531027</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0015435835351089277 +/- 0.0006268860525789536</t>
+          <t>-0.000242130750605285 +/- 0.0005028222677311015</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-0.0016343825665859457 +/- 0.0005447941888619942</t>
+          <t>-0.00042372881355926537 +/- 0.0004529851557837616</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.000605326876513268 +/- 0.0012030633725394575</t>
+          <t>-0.01262106537530261 +/- 0.0012110320232289692</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.007506053268765111 +/- 0.0019837735603116173</t>
+          <t>-0.007627118644067754 +/- 0.0019698716822364295</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.0006658595641646725 +/- 0.0002965483950100527</t>
+          <t>0.0034200968523002916 +/- 0.000384036850497872</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0.0007869249394673484 +/- 0.00132066732622708</t>
+          <t>0.0010290556900726777 +/- 0.0008792880778652316</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.010472154963680369 +/- 0.0016916693235450345</t>
+          <t>-0.004963680387409164 +/- 0.0009100058340419352</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.000302663438256634 +/- 0.001048456905308035</t>
+          <t>0.00033292978208235844 +/- 0.0005320337721321817</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.001967312348668304 +/- 0.0008798088289194146</t>
+          <t>0.0015133171912833365 +/- 0.0006767760222456888</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.001119854721549607 +/- 0.0014069781233861218</t>
+          <t>0.0012106537530266915 +/- 0.0013192793412653344</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.00687046004842613 +/- 0.0012915610347065535</t>
+          <t>-0.0001210653753026314 +/- 0.0012196998595405356</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0.0029358353510896217 +/- 0.0012185727687165546</t>
+          <t>0.000635593220339048 +/- 0.0013565941181001722</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>3.026634382570226e-05 +/- 0.0002855321165876599</t>
+          <t>0.00021186440677968267 +/- 0.00013869781159068728</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.0005750605326876768 +/- 0.0011033732526366778</t>
+          <t>-0.0011198547215495957 +/- 0.0009765294070763756</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.0013922518159806608 +/- 0.0011737723625705222</t>
+          <t>-0.0011501210653752536 +/- 0.001081148371639935</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-0.001906779661016933 +/- 0.0008983548474368133</t>
+          <t>-0.0005145278450362723 +/- 0.0003041729909540344</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.0016646489104116479 +/- 0.0018272952600633836</t>
+          <t>0.00054479418886203 +/- 0.001303913996884869</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.00272397094430995 +/- 0.0014388455598068424</t>
+          <t>-0.0006961259079902749 +/- 0.0010488936713779345</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.0022094430992736004 +/- 0.0007662826211363345</t>
+          <t>-0.003389830508474523 +/- 0.001651111585591506</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>0.00015133171912836695 +/- 0.00045399515738497507</t>
+          <t>-0.00021186440677961604 +/- 0.0002723970944309737</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.0005750605326876101 +/- 0.0009614031582487152</t>
+          <t>0.0003026634382566895 +/- 0.0004060656133474195</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.00027239709443100947 +/- 0.0003159899064440338</t>
+          <t>-0.0010895883777239045 +/- 0.0007187858406197347</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-3.0266343825635644e-05 +/- 0.00043755545686441366</t>
+          <t>3.026634382570226e-05 +/- 0.0005489817538504126</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.005478208232445536 +/- 0.0011912027030359712</t>
+          <t>-0.0017251815980629192 +/- 0.0014518383723016114</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.00027239709443100947 +/- 0.0005969456090591888</t>
+          <t>-0.00021186440677962716 +/- 0.00030417299095400344</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.0017554479418885772 +/- 0.0009059703115675252</t>
+          <t>-0.0016949152542372393 +/- 0.000977935497663658</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0015435835351089388 +/- 0.0018728484872160944</t>
+          <t>0.0008474576271186973 +/- 0.0008211053248335671</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0006053268765132902 +/- 0.0006202754700944104</t>
+          <t>0.0005145278450363611 +/- 0.0004071920111100017</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.00208837772397098 +/- 0.0009518271908908081</t>
+          <t>0.0003026634382567006 +/- 0.001124344771247372</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.002633171912832888 +/- 0.0011803874092009626</t>
+          <t>-0.0011501210653752313 +/- 0.0011627949583715934</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.0025423728813559034 +/- 0.0013549049204358164</t>
+          <t>-0.0020581113801452335 +/- 0.0008751109137288666</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.0003796267004112508 +/- 0.0010473233380098924</t>
+          <t>0.0020879468522619904 +/- 0.000751302884342775</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00313192027839293 +/- 0.001062973591674213</t>
+          <t>0.004618791521670373 +/- 0.0013135425176859735</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0010756089844985773 +/- 0.0006514160165129613</t>
+          <t>0.002689022461246471 +/- 0.0010704792354120924</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0013919645681746528 +/- 0.0009822318694248861</t>
+          <t>0.0018981335020563429 +/- 0.0010681393872909862</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.003321733628598544 +/- 0.0012025674032741878</t>
+          <t>0.0016134134767479048 +/- 0.0005378044922493059</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0036380892122745865 +/- 0.001336578941744848</t>
+          <t>-0.002783929136349228 +/- 0.001037723471487313</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0002847200253084381 +/- 0.00017036269557527177</t>
+          <t>0.0005061689338816677 +/- 0.00020984655427746282</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.0030686491616576995 +/- 0.00111445206920649</t>
+          <t>-0.0016766845934830354 +/- 0.0013200029133201392</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.00993356532742804 +/- 0.0017625293612380886</t>
+          <t>0.00737108509965202 +/- 0.002311994481568311</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9.49066751028127e-05 +/- 0.002281491899032301</t>
+          <t>0.007750711800063303 +/- 0.0022020257583416445</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.00012654223347040582 +/- 0.0010319206852451718</t>
+          <t>-0.005124960455552041 +/- 0.0013919645681746374</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0005061689338816677 +/- 0.000737861676032284</t>
+          <t>-0.000284720025308427 +/- 0.0010535163432677298</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.0003796267004112619 +/- 0.0010568360068642783</t>
+          <t>-0.0011705156596013677 +/- 0.0012736995975449307</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.03881683011705156 +/- 0.0023591304254985297</t>
+          <t>0.04185384372034168 +/- 0.002899619398418785</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.001075608984498566 +/- 0.0014091146758190456</t>
+          <t>0.003638089212274609 +/- 0.002330104375617878</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.006516925023726661 +/- 0.0010415740356314149</t>
+          <t>-0.0013286934514393778 +/- 0.0013847560030521523</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.004555520404935143 +/- 0.0012590793256648137</t>
+          <t>0.0008225245175577766 +/- 0.0012511053421882434</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0011072445428661926 +/- 0.0009827411937367463</t>
+          <t>0.0003479911420436577 +/- 0.0006995679970735771</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.0008225245175577211 +/- 0.0010024030065014069</t>
+          <t>0.005789307181271764 +/- 0.0009282759095932565</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00025308446694083386 +/- 0.00018981335020562537</t>
+          <t>0.0003796267004112508 +/- 0.00012654223347041693</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.006706738373932319 +/- 0.001599395717781019</t>
+          <t>0.0036064536539070157 +/- 0.0021926888264680025</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.0011072445428661926 +/- 0.0012190983149634824</t>
+          <t>0.00319519139512815 +/- 0.0012125129956809004</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.0034482758620689837 +/- 0.0011790348088316323</t>
+          <t>0.0036064536539069936 +/- 0.0009081113631386833</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0022144890857323297 +/- 0.0008127322099756674</t>
+          <t>0.0011388801012337968 +/- 0.0007774884990474466</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0015185068016450142 +/- 0.0013332051569569926</t>
+          <t>0.002467573552673241 +/- 0.0009036923035169419</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.00031635558367604233 +/- 0.0002450479814114078</t>
+          <t>-0.00034799114204364656 +/- 0.00035931087287567875</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.008415058525782993 +/- 0.0018073846070339513</t>
+          <t>0.006896551724137956 +/- 0.0007851739099013509</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.004175893704523892 +/- 0.0010568360068642876</t>
+          <t>0.004966782663714031 +/- 0.0012736995975449255</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.0023726668775704064 +/- 0.001329070011869656</t>
+          <t>0.012274596646630831 +/- 0.0009781477275381538</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.004049351471053464 +/- 0.000562365986543229</t>
+          <t>0.007560898449857656 +/- 0.0009847758567714919</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.163555836760423e-05 +/- 0.00033028492593831807</t>
+          <t>0.0002847200253084381 +/- 0.0002984492607420537</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00015817779183802116 +/- 0.00043029011416434774</t>
+          <t>0.00022144890857322963 +/- 0.00024708160948770706</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.00949066751028157 +/- 0.0013120178015392453</t>
+          <t>0.006959822840873153 +/- 0.0014076934806255556</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.005219867130654876 +/- 0.001498938024736745</t>
+          <t>0.004270800379626715 +/- 0.0009196103672096734</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.0005694400506168762 +/- 0.0002757924038937388</t>
+          <t>0.00012654223347041693 +/- 0.0001549819514573302</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0009490667510281492 +/- 0.0004900959628228442</t>
+          <t>0.00031635558367604233 +/- 0.00042443555409675207</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.00202467573552676 +/- 0.0007902559947356512</t>
+          <t>0.007719076241695688 +/- 0.0009923686897411142</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>0.0012337867763365872 +/- 0.0009847758567714919</t>
+          <t>0.0016766845934831354 +/- 0.0003479911420436466</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.0025941157861436247 +/- 0.0004196931085549641</t>
+          <t>-0.0018664979436886608 +/- 0.0006552456557167999</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.003891173679215443 +/- 0.0009389953862483808</t>
+          <t>0.003954444795950673 +/- 0.0011942161397138175</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.003479911420436588 +/- 0.001456610494555059</t>
+          <t>0.002056311293894364 +/- 0.0014094697507083468</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.002594115786143658 +/- 0.0007045573379095038</t>
+          <t>0.0014868712432774766 +/- 0.0006491073878103063</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.0016134134767478603 +/- 0.0012125129956809253</t>
+          <t>0.0014552356849098613 +/- 0.0009923686897411199</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.00022144890857322963 +/- 0.0011584836079468524</t>
+          <t>-0.0036064536539069823 +/- 0.000681450782301115</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.001297057893071829 +/- 0.0011790348088316603</t>
+          <t>0.004808604871875999 +/- 0.0006755506644752714</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.003954444795950629 +/- 0.0010890170501776822</t>
+          <t>0.002087946852261957 +/- 0.0011597787269739617</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.0006643467257196889 +/- 0.0003302849259383181</t>
+          <t>0.00015817779183802116 +/- 0.00025505402557096825</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.00044289781714644815 +/- 0.000992368689741095</t>
+          <t>0.0030686491616577103 +/- 0.0011144520692064782</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.002087946852261979 +/- 0.0009719893385471171</t>
+          <t>0.007307813982916833 +/- 0.0014528266375457117</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.0030686491616576882 +/- 0.0010497095870317713</t>
+          <t>0.004460613729832352 +/- 0.001345534344709693</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.0006010756089844915 +/- 0.0013603290098070054</t>
+          <t>0.0013603290098070596 +/- 0.0012009017966531082</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0003796267004112508 +/- 0.000368930838016142</t>
+          <t>0.00015817779183802116 +/- 0.00045295226394419236</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.00041126225877885503 +/- 0.00042561290879700425</t>
+          <t>0.0013603290098070596 +/- 0.0004256129087970447</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0005293641420652011</t>
+          <t>0.00012654223347041693 +/- 0.00028994468174348</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.0001898133502056476 +/- 0.0010221761734516609</t>
+          <t>0.0012021512179690164 +/- 0.0008925489389222527</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.0017715912685859036 +/- 0.0017738495120374947</t>
+          <t>0.0034482758620689837 +/- 0.001603457880097965</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.00012654223347041693 +/- 0.00020984655427746282</t>
+          <t>-0.0007276178424548974 +/- 0.00042561290879700425</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.0018032268269534747 +/- 0.0011322701783089797</t>
+          <t>-0.003827902562480212 +/- 0.0008303957449165812</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.0014552356849098168 +/- 0.0012982147756205706</t>
+          <t>0.003416640303701368 +/- 0.0011388801012337524</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6.327111673520847e-05 +/- 0.0004428978171464592</t>
+          <t>0.0013919645681746752 +/- 0.0004518461517585005</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.003258462511863347 +/- 0.0008133476831497661</t>
+          <t>0.002878835811452085 +/- 0.0009745600633185223</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.0006643467257197222 +/- 0.0012610649432454788</t>
+          <t>0.00620056944005064 +/- 0.0009923686897410921</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.0014552356849098058 +/- 0.0014161992588167772</t>
+          <t>0.004492249288199956 +/- 0.0010756089844985903</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.004587155963302725 +/- 0.0011773359105301108</t>
+          <t>-0.0009807023093957312 +/- 0.0014528266375457173</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-0.0001898133502056254 +/- 0.00015498195145733024</t>
+          <t>0.0003796267004112508 +/- 0.0003099639029146605</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.0006010756089844915 +/- 0.0012289101296776188</t>
+          <t>0.002087946852261979 +/- 0.0010024030065014077</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.00041126225877887725 +/- 0.0011925388690269302</t>
+          <t>-0.002815564694716821 +/- 0.0011705156596014058</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0010439734261309618 +/- 0.0007220950465367589</t>
+          <t>-0.001360329009806982 +/- 0.0004911159347124187</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.0017399557102182883 +/- 0.0012594766996137043</t>
+          <t>-0.0011388801012337524 +/- 0.001328693451439412</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.00025308446694083386 +/- 0.0007324161279841743</t>
+          <t>-0.0011705156596013566 +/- 0.0007080996294083744</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.004428978171464715 +/- 0.0014566104945550637</t>
+          <t>0.0035431825371718072 +/- 0.001333205156956996</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>6.327111673520847e-05 +/- 0.00018981335020562537</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.0003796267004112508 +/- 0.0006295396628323884</t>
+          <t>0.0003479911420436577 +/- 0.0006995679970735822</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-9.49066751028127e-05 +/- 0.0006335015626225934</t>
+          <t>0.0002847200253084492 +/- 0.0006239507410096797</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,52 +3936,52 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.0006643467257196889 +/- 0.0006397895734310685</t>
+          <t>0.0006327111673521069 +/- 0.0005479439441850448</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.0006959822840873042 +/- 0.0009984013817184022</t>
+          <t>-0.006232204998418212 +/- 0.0013275631292855097</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0005694400506168762 +/- 0.00012654223347041693</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.00025308446694083386 +/- 0.00036893083801614195</t>
+          <t>-0.0006010756089844804 +/- 0.0005561023673282637</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.00031635558367606456 +/- 0.001166661747205675</t>
+          <t>0.0007592534008225126 +/- 0.0008744242303755301</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>-0.004713698196773153 +/- 0.0008059309840466241</t>
+          <t>0.0066434672571971 +/- 0.0008249544328000827</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0.002372666877570417 +/- 0.0007651620767129254</t>
+          <t>-0.00044289781714645926 +/- 0.0008857956342929185</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.00041126225877887725 +/- 0.0013647361347752537</t>
+          <t>-0.0011705156596013566 +/- 0.0007755552465758236</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-0.00012654223347038362 +/- 0.0016632001807143147</t>
+          <t>0.003416640303701368 +/- 0.0007723224052979016</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.000790888959190128 +/- 0.0007651620767129368</t>
+          <t>0.0015185068016450697 +/- 0.0007186217457513926</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.007870081199250445 +/- 0.0012159851551487382</t>
+          <t>-0.002248594628357292 +/- 0.0010890440833330928</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.002498438475952547 +/- 0.0006698191939265261</t>
+          <t>0.0004059962523422889 +/- 0.0011350894344401233</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.007245471580262353 +/- 0.001515885209183181</t>
+          <t>-0.00246720799500314 +/- 0.0011212569063720403</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0015615240474703418 +/- 0.0012255725715395827</t>
+          <t>-0.00621486570893196 +/- 0.001298602303953275</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0021861336664584785 +/- 0.0013541213859262304</t>
+          <t>0.004247345409119241 +/- 0.0013910716709131588</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0015615240474703418 +/- 0.0016760034809492606</t>
+          <t>0.0003747657713928709 +/- 0.0010526108398721094</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00021861336664584784 +/- 0.0004642744768057029</t>
+          <t>-0.0005309181761399163 +/- 0.00031386244912932416</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0015615240474703418 +/- 0.0006550960950469449</t>
+          <t>0.0008432229856339624 +/- 0.0015492962841739317</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.01114928169893814 +/- 0.002494727099755341</t>
+          <t>0.018738288569643935 +/- 0.00395777811678721</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.01470955652717052 +/- 0.003949019912960226</t>
+          <t>0.022423485321673896 +/- 0.003333917837622123</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007089319175515296 +/- 0.0012728097359346816</t>
+          <t>0.0008744534665833914 +/- 0.0008921209779566395</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0020299812617114443 +/- 0.0009998632475691587</t>
+          <t>0.0008432229856339846 +/- 0.0010268133805605064</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.00031230480949406836 +/- 0.0009369144284822051</t>
+          <t>-0.000374765771392882 +/- 0.00148336565734391</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.004903185509056851 +/- 0.0036662243603883464</t>
+          <t>0.005371642723297898 +/- 0.004042628638422072</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.010836976889444072 +/- 0.002186356729942173</t>
+          <t>0.0179575265459088 +/- 0.002105453315513176</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.0010930668332292393 +/- 0.0016832620834743234</t>
+          <t>-0.0035602748282323794 +/- 0.001376977369459635</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.000749531542785764 +/- 0.001250779787289252</t>
+          <t>-0.0009369144284822161 +/- 0.0019553373944407827</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.002841973766396022 +/- 0.0013060914220066602</t>
+          <t>0.00021861336664584784 +/- 0.0010549247816398909</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.002061211742660851 +/- 0.0011618410517013368</t>
+          <t>0.0022485946283572365 +/- 0.0011242973141785998</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0005933791380387299 +/- 0.0003812166026150465</t>
+          <t>-0.0008119925046845778 +/- 0.00031848966355982637</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.004059962523422889 +/- 0.0016046511653548055</t>
+          <t>0.010399750156152365 +/- 0.0019152714686398585</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.007713928794503477 +/- 0.0008948500176073811</t>
+          <t>-0.0018738288569644101 +/- 0.001444726234381069</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.00021861336664584784 +/- 0.0010823062742763006</t>
+          <t>0.002404747033104282 +/- 0.0010456382912418843</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.0014366021236727144 +/- 0.001446075815464123</t>
+          <t>0.002217364147407841 +/- 0.0012211876824495024</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0055277951280449985 +/- 0.0012018664212925453</t>
+          <t>0.002935665209244176 +/- 0.001304223174129947</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.000374765771392882 +/- 0.00041431914932609903</t>
+          <t>0.001155527795128053 +/- 0.0005235182577838952</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.006995627732667098 +/- 0.002701752498923423</t>
+          <t>0.004778263585259135 +/- 0.0012417798471000112</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0010451718007921066</t>
+          <t>-0.0009993753903810188 +/- 0.0008921209779566395</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-0.0032167395377889043 +/- 0.0014382984309393547</t>
+          <t>0.000374765771392882 +/- 0.0013308729389545698</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.007682698313554059 +/- 0.0014728077604686343</t>
+          <t>-0.002904434728294836 +/- 0.0016646168608665235</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.00046845721424110254 +/- 0.0002879308075356949</t>
+          <t>-9.36914428482205e-05 +/- 0.0004642744768057029</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.0004059962523422889 +/- 0.00042016314950261724</t>
+          <t>0.0010930668332292393 +/- 0.0005083953965053036</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.006277326670830774 +/- 0.001420557828300342</t>
+          <t>-0.001905059337913817 +/- 0.0013645254387853608</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.0031542785758900903 +/- 0.0012527277401706257</t>
+          <t>0.0 +/- 0.0012570026107119455</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-0.0004059962523422889 +/- 0.00046427447680570286</t>
+          <t>-0.0006246096189881367 +/- 0.0004190008702373151</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.0006246096189881367 +/- 0.000503576374034891</t>
+          <t>0.0021861336664584117 +/- 0.0007900756177809389</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.007807620237351642 +/- 0.002118154273305802</t>
+          <t>0.0030293566520923853 +/- 0.0009269720224644103</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>-0.0014366021236727144 +/- 0.0008964834537418752</t>
+          <t>-0.00246720799500314 +/- 0.001434223922948796</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.000374765771392882 +/- 0.00041431914932609903</t>
+          <t>-0.0002498438475952547 +/- 0.0005724641717621326</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.0024359775140537334 +/- 0.001345450295349042</t>
+          <t>0.0040287320424733705 +/- 0.0008772374706551053</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.0054965646470956035 +/- 0.0011190801291173667</t>
+          <t>0.00021861336664583675 +/- 0.0014315011413323893</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0011867582760774597 +/- 0.0013812207612427315</t>
+          <t>0.003216739537788804 +/- 0.0007656246516009391</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.012492192379762623 +/- 0.001471482696988111</t>
+          <t>0.0021236727045596203 +/- 0.0009856173540324067</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.007307932542161133 +/- 0.002015273679562949</t>
+          <t>0.005434103685196678 +/- 0.0013410937260202396</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.004809494066208652 +/- 0.0015502403055578943</t>
+          <t>0.004341036851967439 +/- 0.0010493627493074053</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.003622735790131193 +/- 0.001250779787289252</t>
+          <t>-0.0048407245471580596 +/- 0.0008860875052536668</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0004059962523422889 +/- 0.0003962703791520802</t>
+          <t>0.002186133666458423 +/- 0.0006698191939264795</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.003685196752030007 +/- 0.0009856173540324553</t>
+          <t>0.004434728294815671 +/- 0.0013308729389545511</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.002998126171143056 +/- 0.0008286382986521981</t>
+          <t>0.0012179887570268222 +/- 0.0013787470365173944</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.001124297314178646 +/- 0.0015875409153202902</t>
+          <t>0.00015615240474702307 +/- 0.00160617000257635</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.0003435352904434752 +/- 0.002026133864248433</t>
+          <t>-0.0009993753903810188 +/- 0.0014501170226413466</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.001967520299812631 +/- 0.0004201631495026172</t>
+          <t>-0.000187382885696441 +/- 0.0003999452990276635</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.0006870705808869504 +/- 0.0005188397166095023</t>
+          <t>-6.246096189881367e-05 +/- 0.0004372267332916957</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0003435352904434752 +/- 0.00016818128691863026</t>
+          <t>0.000374765771392882 +/- 0.0004143191493260991</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.016114928169893815 +/- 0.001326468493541252</t>
+          <t>-0.0024359775140537334 +/- 0.0013381814669349592</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0018425983760150034 +/- 0.000982147732262117</t>
+          <t>0.00640224859462829 +/- 0.001203488374016104</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0004996876951905094 +/- 0.000374765771392882</t>
+          <t>0.0006246096189881367 +/- 0.0005758616150713898</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.0038725796377264477 +/- 0.0009389941523031237</t>
+          <t>0.0054653341661460965 +/- 0.0024241372105340392</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.0009681449094316119 +/- 0.001718811730895329</t>
+          <t>0.009150530918176091 +/- 0.0009477820678009758</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-6.246096189881367e-05 +/- 0.00023370751947370186</t>
+          <t>-9.36914428482205e-05 +/- 0.0006558400999375436</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.003903810118675843 +/- 0.0015251861895158843</t>
+          <t>-0.0023422860712055127 +/- 0.0012115655678495289</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.005496564647095592 +/- 0.0016419037386751862</t>
+          <t>-0.0029356652092442427 +/- 0.0015312493032019173</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.01311680199875076 +/- 0.0012014605909851017</t>
+          <t>0.005527795128044899 +/- 0.0013900195555445372</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.0004372267332916957 +/- 0.00078013716407226</t>
+          <t>0.0021861336664584343 +/- 0.0008722198653197003</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-0.00012492192379762735 +/- 0.00015299748549551498</t>
+          <t>-0.00031230480949406836 +/- 0.0002793339134915434</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.0007807620237351709 +/- 0.0010750727344196517</t>
+          <t>-0.0035290443472829726 +/- 0.00048482744210681227</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.002279825109306699 +/- 0.0006095946688302083</t>
+          <t>0.0013429106808244828 +/- 0.000541828593781906</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.00031230480949406836 +/- 0.0005225859003960533</t>
+          <t>-3.123048094940684e-05 +/- 0.0004726029341168539</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.004747033104309839 +/- 0.0008472617093223379</t>
+          <t>0.0014678326046221213 +/- 0.0005595400645586833</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.0010306058713304255 +/- 0.0010456382912419314</t>
+          <t>0.0017801374141161563 +/- 0.0006990327696938929</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-0.002998126171143056 +/- 0.0008518539473445316</t>
+          <t>-0.0024359775140537334 +/- 0.0009554689906794791</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>3.123048094940684e-05 +/- 9.369144284822049e-05</t>
+          <t>3.123048094940684e-05 +/- 0.00016818128691863026</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.00015615240474703418 +/- 0.0003760647900934534</t>
+          <t>0.00012492192379762735 +/- 0.0008518539473445317</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-6.246096189881367e-05 +/- 0.0004797717518968558</t>
+          <t>0.00046845721424110254 +/- 0.000488834348610201</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.0002498438475952547 +/- 0.000414319149326099</t>
+          <t>-9.36914428482205e-05 +/- 0.0005595400645586833</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.002841973766396022 +/- 0.0008991992535220529</t>
+          <t>0.0002498438475952547 +/- 0.0009348300778948076</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>9.36914428482205e-05 +/- 0.00031386244912932416</t>
+          <t>-0.0014053716427233076 +/- 0.0002879308075356949</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0008119925046845778 +/- 0.0012191893376604166</t>
+          <t>0.0004059962523422889 +/- 0.0007656246516009585</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.002248594628357292 +/- 0.00103391288927214</t>
+          <t>-0.0025608994378513604 +/- 0.0006955358354565972</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.00021861336664584784 +/- 0.0002439178537135137</t>
+          <t>-0.0006246096189881367 +/- 0.00024191026522220134</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.001967520299812631 +/- 0.0008948500176074017</t>
+          <t>-0.0025921299188007675 +/- 0.0011350894344401231</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.0004996876951905094 +/- 0.0007011225584211057</t>
+          <t>-0.0002810743285446615 +/- 0.0014067589793323278</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.0024359775140537334 +/- 0.0008921209779566395</t>
+          <t>-0.0007183010618363572 +/- 0.00048482744210681227</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0005686920083807223 +/- 0.0004114853961349139</t>
+          <t>0.001406764441783892 +/- 0.0006961809847119406</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.0009877282250823072 +/- 0.0005993709785842776</t>
+          <t>-0.0002993115833582749 +/- 0.0008251450914151555</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0003591739000299299 +/- 0.000624980934385544</t>
+          <t>0.007333133792277835 +/- 0.001846293985428463</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.005208021550433995 +/- 0.001372923668504025</t>
+          <t>0.0010176593834181347 +/- 0.0008695503769131337</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.0019155941334929594 +/- 0.0006163202718339996</t>
+          <t>0.0074528584256211335 +/- 0.0015288348146210522</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.00014965579167913745 +/- 0.0012359067837211916</t>
+          <t>0.01050583657587556 +/- 0.0011393514702588575</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00014965579167913745 +/- 0.00020078431405265925</t>
+          <t>0.0 +/- 0.0001893012666966997</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.0011074528584256171 +/- 0.00053626078620679</t>
+          <t>0.002065249925172097 +/- 0.0010911539140112613</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.026339419335528302 +/- 0.0031420588978175786</t>
+          <t>0.025261897635438513 +/- 0.0035672114733168577</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.016162825501346956 +/- 0.0032375497834157226</t>
+          <t>0.017689314576474158 +/- 0.0033422531158091</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.0011373840167614446 +/- 0.0008858813880244651</t>
+          <t>-0.0005088296917090673 +/- 0.0009181599311689861</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0006884166417240323 +/- 0.0006564415504178758</t>
+          <t>0.005357677342113154 +/- 0.0006884166417240724</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.002454354983537854 +/- 0.0006799052194912007</t>
+          <t>0.004788985333732421 +/- 0.001520314289039277</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.017330140676444228 +/- 0.0027316179343628427</t>
+          <t>0.019066147859922222 +/- 0.0033758578463029777</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.007422927267285262 +/- 0.001536725250283604</t>
+          <t>0.012092187967674417 +/- 0.001392361969423881</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.0011074528584256171 +/- 0.0007458806222314917</t>
+          <t>0.003412152050284334 +/- 0.0008053651030873189</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.0008380724334031697 +/- 0.0007183478000598598</t>
+          <t>-0.0017360071834779944 +/- 0.0008444618964181882</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.0005088296917090673 +/- 0.0005993709785842776</t>
+          <t>0.002184974558515407 +/- 0.0009657148042443354</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0005686920083807223 +/- 0.00041148539613491383</t>
+          <t>-0.0035618078419634713 +/- 0.0009220545825051966</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-2.993115833582749e-05 +/- 0.00016118422050686877</t>
+          <t>8.979347500748247e-05 +/- 0.00013716179871163794</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.0010775217000897896 +/- 0.0011684658064018598</t>
+          <t>-0.005447470817120603 +/- 0.0012106404319758525</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0020951810835079243 +/- 0.0005834656896024501</t>
+          <t>-0.0013768332834480645 +/- 0.0008591858781447036</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-0.0003591739000299299 +/- 0.0006799052194912007</t>
+          <t>-2.993115833582749e-05 +/- 0.0005261417489149023</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.0008380724334031697 +/- 0.0004598111791600468</t>
+          <t>0.0009877282250823072 +/- 0.001338896692388205</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.00023944926668661992 +/- 0.0009633928128962002</t>
+          <t>-0.0024842861418736817 +/- 0.0008036947968929964</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.00020951810835079243 +/- 0.00019165292539457727</t>
+          <t>-0.0003292427416941024 +/- 0.0004114853961349139</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0018557318168213044 +/- 0.0014216512525636485</t>
+          <t>0.0019155941334929594 +/- 0.0014366956001197195</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.002574079616881164 +/- 0.000601608836942284</t>
+          <t>-0.001287039808440582 +/- 0.001159615122885989</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.002394492666866199 +/- 0.0006692810468421974</t>
+          <t>-0.0018557318168213044 +/- 0.0008444618964181882</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.001466626758455547 +/- 0.0005088296917090673</t>
+          <t>-0.0044298114337024685 +/- 0.0006665985468817722</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0007482789583956873 +/- 0.0002413127132085759</t>
+          <t>-8.979347500748247e-05 +/- 0.00019165292539457727</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.00041903621670158486 +/- 0.00023944926668661995</t>
+          <t>2.993115833582749e-05 +/- 0.0002095181083507924</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,272 +4606,272 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.0006584854833882048 +/- 0.0006249809343855441</t>
+          <t>-0.002693804250224474 +/- 0.000613406211670731</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0011373840167614446 +/- 0.0008444618964181883</t>
+          <t>0.00044896737503741235 +/- 0.0010303450750109816</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>0.0002993115833582749 +/- 0.0001893012666966997</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>0.0007183478000598598 +/- 0.000601608836942284</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>0.0011972463334330996 +/- 0.0008359317595791015</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>-0.0008680035917389972 +/- 0.0007969785666383898</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-0.0009278659084106522 +/- 0.0005088296917090673</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.0011373840167614446 +/- 0.0008229707922698278</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.003232565100269369 +/- 0.000855004900154783</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.006554923675546309 +/- 0.0014131184237190166</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-0.004579467225381606 +/- 0.0006831913924282122</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.0023046991918587167 +/- 0.001071267893934344</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.0032026339419335415 +/- 0.0006831913924282122</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>-0.0011074528584256171 +/- 0.000781082810577662</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>-0.00014965579167913745 +/- 0.0003604188739536741</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0020353187668362693 +/- 0.000624980934385544</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>-0.00014965579167913745 +/- 0.0013063844862493336</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.0029631846752469215 +/- 0.001314587923136646</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>0.0009577970667464797 +/- 0.0006799052194912007</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-0.00047889853337323984 +/- 0.0004675396393838149</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>-0.0011972463334330996 +/- 0.0003786025333933994</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.00041903621670158486 +/- 0.00019854084348131627</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>-0.0037413947919784363 +/- 0.001113905660935548</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.0017360071834779944 +/- 0.001446638248858968</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>-0.00017958695001496494 +/- 0.00027432359742327587</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>-0.0003292427416941024 +/- 0.0009220545825051966</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>-0.001586351391798857 +/- 0.0006426492233937088</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-2.993115833582749e-05 +/- 0.0002486268740771639</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.0009877282250823072 +/- 0.0006831913924282123</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.001825800658485477 +/- 0.0006884166417240323</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0003591739000299299 +/- 0.001094023758305717</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.001825800658485477 +/- 0.0006199435850705749</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>-0.0007782101167315147 +/- 0.0005218675777959483</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>0.0016162825501346845 +/- 0.0004675396393838148</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0006884166417240323 +/- 0.00042434740732588374</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>0.00047889853337323984 +/- 0.00038330585078915453</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-0.0011074528584256171 +/- 0.0005842329032009298</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>0.002753666566896129 +/- 0.001489357115190025</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>-0.00047889853337323984 +/- 0.0004479685587277974</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.0006884166417240323 +/- 0.00040268255154365945</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-0.0022149057168512343 +/- 0.0013398999871654781</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-0.0018856629751571319 +/- 0.0012631516220298785</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>0.0025441484585453367 +/- 0.00046849673278953825</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0.00023944926668661992 +/- 0.00011972463334330997</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0.0005088296917090673 +/- 0.0007924694579391607</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0.003172702783597714 +/- 0.0011912450608878974</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0.0006285543250523773 +/- 0.0008191518816763819</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.0017958695001496494 +/- 0.0005986231667165498</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0.0023046991918587167 +/- 0.000519286188952332</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>0.0038311882669859187 +/- 0.0007057663048519338</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0001338562093684395</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0011673151750972721 +/- 0.0004327097364501918</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.001526489075127202 +/- 0.0005591601823486781</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>0.002065249925172097 +/- 0.0007856572731760933</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-0.00023944926668661992 +/- 0.0007428718135881959</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-0.00017958695001496494 +/- 0.00027432359742327587</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>0.00038910505836575737 +/- 0.0005993709785842775</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>-5.986231667165498e-05 +/- 0.00026093378889797416</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>0.0011673151750972721 +/- 0.0005749587761837317</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>0.0033822208919485064 +/- 0.0006831913924282123</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
         <is>
           <t>2.993115833582749e-05 +/- 8.979347500748247e-05</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>0.0008081412750673422 +/- 0.0005527143164507429</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>0.0002693804250224474 +/- 0.0005429020397251419</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-8.979347500748247e-05 +/- 0.0003554128131409122</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>0.0009577970667464797 +/- 0.0005803866934949192</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>0.0006584854833882048 +/- 0.000855004900154783</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>-0.00023944926668661992 +/- 0.00026093378889797416</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-0.0009278659084106522 +/- 0.0007386388913051794</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>0.00017958695001496494 +/- 0.0008899173150145737</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-0.00020951810835079243 +/- 0.00053626078620679</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>0.0009278659084106522 +/- 0.0005749587761837317</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0001338562093684395</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.0013169709667764096 +/- 0.0004675396393838148</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.0007482789583956873 +/- 0.0005052961094323278</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-5.986231667165498e-05 +/- 0.00032236844101373753</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0006692810468421974</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0.0023645615085303717 +/- 0.0008823348083198816</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>0.002993115833582749 +/- 0.0012121195289623774</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>2.993115833582749e-05 +/- 8.979347500748247e-05</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>-0.00011972463334330996 +/- 0.00027432359742327587</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>-0.0003591739000299299 +/- 0.00026093378889797416</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2.993115833582749e-05 +/- 0.0002095181083507924</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>0.0003591739000299299 +/- 0.0005149551192482847</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-8.979347500748247e-05 +/- 0.00019165292539457727</t>
+          <t>0.0011074528584256171 +/- 0.0005017376418509473</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0005686920083807223 +/- 0.0009601325909814656</t>
+          <t>-0.0023645615085303717 +/- 0.0004529406150979199</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.0026040107752169916 +/- 0.0011203212973488676</t>
+          <t>0.0016162825501346845 +/- 0.0007108256262818244</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.00017958695001496494 +/- 0.0001466321306664573</t>
+          <t>0.0005686920083807223 +/- 0.0002095181083507924</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.001227177491768927 +/- 0.0006053202159879261</t>
+          <t>0.001406764441783892 +/- 0.00053626078620679</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.0021550434001795793 +/- 0.0005956225304439487</t>
+          <t>0.00431008680035917 +/- 0.0006851555308147219</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.0002993115833582749 +/- 0.0005008440745489809</t>
+          <t>0.003172702783597714 +/- 0.0011837006844229343</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.001826484018264829 +/- 0.001896184048998171</t>
+          <t>-0.002343987823439886 +/- 0.0014854030926947871</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.002557077625570747 +/- 0.0021099206637641833</t>
+          <t>-0.00767123287671233 +/- 0.0014775843043545174</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.01047184170471841 +/- 0.0019643550447368888</t>
+          <t>-0.007610350076103489 +/- 0.002604474841547326</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.009923896499238971 +/- 0.0025801668311010166</t>
+          <t>0.003013698630136985 +/- 0.001798105257305616</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.00021308980213088357 +/- 0.0015162751178584401</t>
+          <t>-0.003926940639269428 +/- 0.0014753876183930157</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.000273972602739736 +/- 0.0010671871015499647</t>
+          <t>0.002374429223744301 +/- 0.001924320320155754</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.0003044140030441511 +/- 0.00023579807282846625</t>
+          <t>-0.00015220700152207556 +/- 0.00039102686693045954</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0028006088280061125 +/- 0.0010788459754440972</t>
+          <t>-0.0010654490106544955 +/- 0.001974002171917615</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.007914764079147618 +/- 0.0018516780914149904</t>
+          <t>-0.003287671232876721 +/- 0.003926350645329951</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.0018873668188736815 +/- 0.002535240525255048</t>
+          <t>-0.01187214611872146 +/- 0.0026573093263677406</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.005540334855403351 +/- 0.0009213239543635641</t>
+          <t>0.002343987823439875 +/- 0.0010895299950181615</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.00048706240487060847 +/- 0.00119615724227632</t>
+          <t>-0.0024048706240487163 +/- 0.0015608455090769203</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.0014916286149162627 +/- 0.0016973640011507586</t>
+          <t>0.0032876712328766987 +/- 0.0010702219684168642</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.021065449010654526 +/- 0.0025534510776877733</t>
+          <t>0.019330289193302885 +/- 0.0018226748712234493</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.006423135464231377 +/- 0.0015003009473791983</t>
+          <t>0.011232876712328765 +/- 0.002150162969425912</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0004566210045662267 +/- 0.0013075635674225042</t>
+          <t>-0.00602739726027397 +/- 0.0015688400276073374</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.00018264840182646847 +/- 0.0009835917455953455</t>
+          <t>-0.0022222222222222365 +/- 0.002055865327842086</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0003348554033485773 +/- 0.0007387921521772699</t>
+          <t>0.0026179604261795885 +/- 0.001047467308011275</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.0038660578386605525 +/- 0.00078264597456208</t>
+          <t>-0.005083713850837146 +/- 0.001255500190398866</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.0003044140030441511 +/- 0.0002722761616438199</t>
+          <t>-0.0006392694063927174 +/- 0.00031781754973853667</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.000852359208523612 +/- 0.0015922918515217138</t>
+          <t>-0.009497716894977182 +/- 0.0013324851524042238</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.0070319634703196465 +/- 0.0011980924599180628</t>
+          <t>-0.004140030441400311 +/- 0.0015293585007099618</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0010958904109589329 +/- 0.0007604259358780475</t>
+          <t>0.00015220700152207556 +/- 0.0011164152706783755</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.003835616438356193 +/- 0.000760425935878067</t>
+          <t>0.0009741248097412502 +/- 0.0013043704892315732</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.002648401826484037 +/- 0.0012180364702430804</t>
+          <t>0.006423135464231344 +/- 0.0012875668786944791</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0003044140030441511 +/- 0.0003601875058203855</t>
+          <t>0.0006392694063927062 +/- 0.0006156392211919798</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.008066971080669717 +/- 0.0016064870382902492</t>
+          <t>0.007153729071537285 +/- 0.0012195571156170524</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.00030441400304414 +/- 0.0009626416012689306</t>
+          <t>-0.005449010654490094 +/- 0.0014816552235784462</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.0077016742770167675 +/- 0.0012480974124809542</t>
+          <t>-0.0025875190258751956 +/- 0.0013286546631838703</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0015220700152207222 +/- 0.0011946068109801307</t>
+          <t>-2.2204460492503132e-17 +/- 0.0017273985947167082</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0006088280060883022 +/- 0.0004715961456569325</t>
+          <t>0.00042617960426181154 +/- 0.0004556051612510293</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.000547945205479472 +/- 0.0005057305243785922</t>
+          <t>0.0014611872146118587 +/- 0.0009009831711992979</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.005875190258751916 +/- 0.00126285957459311</t>
+          <t>-0.004231354642313556 +/- 0.0009076439279071797</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.0024961948249619505 +/- 0.00113738457791595</t>
+          <t>-0.006879756468797582 +/- 0.0014291256735836219</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.00012176560121766045 +/- 0.0004347901630772061</t>
+          <t>-0.00018264840182649066 +/- 0.0008414170448149623</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.00018264840182646847 +/- 0.0008843737623338845</t>
+          <t>0.001887366818873648 +/- 0.0006356350994770394</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.005357686453576882 +/- 0.001148734384420892</t>
+          <t>0.005631659056316574 +/- 0.0011410450419477177</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.0034094368340943926 +/- 0.0007914764079147664</t>
+          <t>-0.0009436834094368352 +/- 0.0015126037441466995</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0002435312024353209 +/- 0.000620885176693208</t>
+          <t>0.00060882800608828 +/- 0.0007701132810151277</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.004322678843226823 +/- 0.0008258544880517893</t>
+          <t>0.004566210045662078 +/- 0.0017273985947167413</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.0010045662100456542 +/- 0.000528138556252556</t>
+          <t>-0.0030441400304414114 +/- 0.0009333156600764781</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.0014003044140030174 +/- 0.0011406389038170566</t>
+          <t>-0.00310502283105023 +/- 0.0020229220975142887</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.011050228310502263 +/- 0.0014281527069394246</t>
+          <t>-0.017351598173515993 +/- 0.001656191233940378</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.00015220700152209776 +/- 0.0009746003405529493</t>
+          <t>-0.0008219178082191969 +/- 0.0016564709723485777</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0009436834094368573 +/- 0.0005175038051750314</t>
+          <t>-0.00797564687975647 +/- 0.0013735785902804954</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.004474885844748843 +/- 0.0009238350627393182</t>
+          <t>-0.0037442922374429253 +/- 0.0010461394385046941</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.0007914764079147929 +/- 0.0005807849019281464</t>
+          <t>0.0004870624048706418 +/- 0.000564603865783625</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.000213089802130928 +/- 0.000817395530112475</t>
+          <t>-0.0024048706240486937 +/- 0.0017082481396162043</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.005814307458143042 +/- 0.002263538684325275</t>
+          <t>-0.018112633181126336 +/- 0.0021057441224378902</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.01796042617960426 +/- 0.0020601429912558483</t>
+          <t>-0.03318112633181125 +/- 0.001982200376998434</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.020882800608827988 +/- 0.0013762745273007493</t>
+          <t>-0.027732115677321166 +/- 0.0016248409309080638</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.00033485540334856625 +/- 0.00048035719446149394</t>
+          <t>-0.0016133942161339564 +/- 0.000817395530112465</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.000578386605783876 +/- 0.0005521569907828642</t>
+          <t>-0.00021308980213090577 +/- 0.0007707146971794596</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-0.000273972602739736 +/- 0.0003457478444931799</t>
+          <t>-0.0013698630136986466 +/- 0.0005139099852704213</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.021278538812785387 +/- 0.001664284558031855</t>
+          <t>-0.019939117199391176 +/- 0.001926486128742374</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.010928462709284603 +/- 0.001988967576732964</t>
+          <t>-0.01735159817351597 +/- 0.0021993780052588685</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-0.0004870624048706196 +/- 0.0005307639505072245</t>
+          <t>3.044140030440401e-05 +/- 0.0008658424750884686</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.0014916286149163072 +/- 0.0010318691784887853</t>
+          <t>-0.004535768645357685 +/- 0.001371215297358325</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.023226788432267876 +/- 0.0018519283012791634</t>
+          <t>-0.02207001522070017 +/- 0.0016407321739070838</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.00060882800608828 +/- 0.0005445523232876026</t>
+          <t>0.00042617960426178937 +/- 0.0008077016232220103</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.003835616438356193 +/- 0.0012929534600666902</t>
+          <t>-0.008127853881278535 +/- 0.0019013085503351238</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.01205479452054794 +/- 0.0015049262824119584</t>
+          <t>-0.03318112633181125 +/- 0.0014850911315251775</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-0.003257229832572273 +/- 0.0014728731084813452</t>
+          <t>-0.00493150684931507 +/- 0.0015747357268039563</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.0030745814307458486 +/- 0.0011097550157417432</t>
+          <t>-0.004596651445966526 +/- 0.0022879704626013455</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-3.0441400304415113e-05 +/- 9.132420091324532e-05</t>
+          <t>0.0003044140030441511 +/- 0.00023579807282846625</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.0035616438356164126 +/- 0.0014728731084813378</t>
+          <t>-0.004048706240487065 +/- 0.0017276668034901304</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.0012785388127853903 +/- 0.0011455030576698188</t>
+          <t>-0.0026179604261795998 +/- 0.001056277112505194</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.0006697108066971103 +/- 0.0004473953868096869</t>
+          <t>-0.0018569254185692551 +/- 0.0013018815695794907</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.010958904109589062 +/- 0.0019348856720938475</t>
+          <t>0.006484018264840163 +/- 0.0013953323149303986</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.0005175038051750014 +/- 0.0011230360271352556</t>
+          <t>-0.004809741248097421 +/- 0.0011852616337249188</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.0016133942161339343 +/- 0.0022577998953776128</t>
+          <t>-0.003348554033485529 +/- 0.0016108074953209053</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0003044140030441511</t>
+          <t>0.00015220700152207556 +/- 0.00020420712123286492</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>3.0441400304415113e-05 +/- 0.0005175038051750568</t>
+          <t>0.0013698630136986356 +/- 0.0011410450419477149</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.000852359208523601 +/- 0.0009313277650397778</t>
+          <t>0.00021308980213090577 +/- 0.0007080489101743337</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,52 +5271,52 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>6.0882800608830226e-05 +/- 0.00042617960426181154</t>
+          <t>-0.000943683409436824 +/- 0.0009765001480879874</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.003561643835616457 +/- 0.0016168367397125666</t>
+          <t>-1.1102230246251566e-17 +/- 0.0009431922913138364</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>9.132420091324533e-05 +/- 0.00019492006811059609</t>
+          <t>-0.0008523592085236231 +/- 0.00012176560121766044</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0004715961456569325</t>
+          <t>0.001187214611872156 +/- 0.0004803571944614496</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.001400304414003073 +/- 0.0013283058891489614</t>
+          <t>-0.00541856925418569 +/- 0.001976582414702938</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0021917808219178215 +/- 0.001865638166946052</t>
+          <t>-0.0027397260273972824 +/- 0.001930090409028603</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.00018264840182651286 +/- 0.0011567732115677475</t>
+          <t>-0.0012480974124809863 +/- 0.000726140666172075</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.006057838660578396 +/- 0.0012947440071925116</t>
+          <t>0.0007305936073059404 +/- 0.0016176962259465963</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.003561643835616457 +/- 0.0016168367397125477</t>
+          <t>-0.006727549467275507 +/- 0.0014816552235784417</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.001217656012176571 +/- 0.0009817056618932763</t>
+          <t>-0.00021308980213091688 +/- 0.0016786990172252417</t>
         </is>
       </c>
     </row>
